--- a/Results/regression_results_formatted.xlsx
+++ b/Results/regression_results_formatted.xlsx
@@ -4849,10 +4849,10 @@
         <v>0.5712506416851921</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>0.04033208121577338</v>
+        <v>0.04033208121577367</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>1.537311246502176e-45</v>
+        <v>1.537311246504306e-45</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>14.16367875064635</v>
+        <v>14.16367875064625</v>
       </c>
     </row>
     <row r="173">
@@ -4875,17 +4875,17 @@
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>-0.0854254663786739</v>
+        <v>-0.08542546637867346</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>0.05359039625199568</v>
+        <v>0.05359039625199507</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>0.1109261101304197</v>
+        <v>0.1109261101304175</v>
       </c>
       <c r="F173" s="3" t="inlineStr"/>
       <c r="G173" s="3" t="n">
-        <v>-1.59404431303291</v>
+        <v>-1.59404431303292</v>
       </c>
     </row>
     <row r="174">
@@ -4900,17 +4900,17 @@
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>0.07620211712330739</v>
+        <v>0.07620211712330763</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>0.05022569897281084</v>
+        <v>0.05022569897281046</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>0.129217771061471</v>
+        <v>0.129217771061467</v>
       </c>
       <c r="F174" s="3" t="inlineStr"/>
       <c r="G174" s="3" t="n">
-        <v>1.517193760997903</v>
+        <v>1.517193760997919</v>
       </c>
     </row>
     <row r="175">
@@ -4925,17 +4925,17 @@
         </is>
       </c>
       <c r="C175" s="3" t="n">
-        <v>0.05621280687420952</v>
+        <v>0.056212806874208</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>0.07901245147808071</v>
+        <v>0.07901245147807981</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>0.4768101421196153</v>
+        <v>0.4768101421196222</v>
       </c>
       <c r="F175" s="3" t="inlineStr"/>
       <c r="G175" s="3" t="n">
-        <v>0.7114423843665176</v>
+        <v>0.7114423843665065</v>
       </c>
     </row>
     <row r="176">
@@ -4950,17 +4950,17 @@
         </is>
       </c>
       <c r="C176" s="3" t="n">
-        <v>0.1635240566744746</v>
+        <v>0.1635240566744808</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>0.1019060632745605</v>
+        <v>0.1019060632745594</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.1085697876392737</v>
+        <v>0.1085697876392566</v>
       </c>
       <c r="F176" s="3" t="inlineStr"/>
       <c r="G176" s="3" t="n">
-        <v>1.604654830340171</v>
+        <v>1.604654830340249</v>
       </c>
     </row>
     <row r="177">
@@ -4975,13 +4975,13 @@
         </is>
       </c>
       <c r="C177" s="5" t="n">
-        <v>-0.2443794261366836</v>
+        <v>-0.2443794261366823</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>0.09669310677598568</v>
+        <v>0.09669310677598594</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0.01149197890510021</v>
+        <v>0.01149197890510086</v>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>-2.527371746393991</v>
+        <v>-2.527371746393971</v>
       </c>
     </row>
     <row r="178">
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>-0.2330187093660425</v>
+        <v>-0.2330187093660412</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>0.06218524918340863</v>
+        <v>0.06218524918340867</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.0001788407812249069</v>
+        <v>0.0001788407812249241</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -5018,32 +5018,36 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>-3.747170147678899</v>
+        <v>-3.747170147678876</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.Pov</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>Poverty Gap Squared</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="n">
-        <v>9.450956638757389e-05</v>
-      </c>
-      <c r="D179" s="3" t="n">
-        <v>6.454702424673197e-05</v>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>0.1431400995325916</v>
-      </c>
-      <c r="F179" s="3" t="inlineStr"/>
-      <c r="G179" s="3" t="n">
-        <v>1.464197110409144</v>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Poverty Gap ($4.20/day)</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>-0.007146346425070877</v>
+      </c>
+      <c r="D179" s="5" t="n">
+        <v>0.003298550144514929</v>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>0.03027213121352595</v>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>-2.166511379841942</v>
       </c>
     </row>
     <row r="180">
@@ -5054,50 +5058,46 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Storm Count (Log)</t>
+          <t>Poverty Gap Squared</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>0.01063704915656689</v>
+        <v>9.450956638757756e-05</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>0.01673396998180213</v>
+        <v>6.454702424672983e-05</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0.5250006322697496</v>
+        <v>0.1431400995325628</v>
       </c>
       <c r="F180" s="3" t="inlineStr"/>
       <c r="G180" s="3" t="n">
-        <v>0.6356560438517863</v>
+        <v>1.464197110409249</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="inlineStr">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.Pov</t>
         </is>
       </c>
-      <c r="B181" s="5" t="inlineStr">
-        <is>
-          <t>Log GDP per Capita (PPP)</t>
-        </is>
-      </c>
-      <c r="C181" s="5" t="n">
-        <v>0.06512696982096272</v>
-      </c>
-      <c r="D181" s="5" t="n">
-        <v>0.02927377044995033</v>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>0.02609768375030449</v>
-      </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G181" s="5" t="n">
-        <v>2.224755090305534</v>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Flood Count (Log)</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>-0.01827645584482767</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>0.01572233068183826</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>0.2450518830497384</v>
+      </c>
+      <c r="F181" s="3" t="inlineStr"/>
+      <c r="G181" s="3" t="n">
+        <v>-1.162452069904611</v>
       </c>
     </row>
     <row r="182">
@@ -5108,104 +5108,104 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Flood Count (Log)</t>
+          <t>Storm Count (Log)</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>-0.01827645584482775</v>
+        <v>0.01063704915656663</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>0.01572233068183825</v>
+        <v>0.01673396998180213</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0.2450518830497357</v>
+        <v>0.5250006322697598</v>
       </c>
       <c r="F182" s="3" t="inlineStr"/>
       <c r="G182" s="3" t="n">
-        <v>-1.162452069904618</v>
+        <v>0.6356560438517707</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.Pov</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Log GDP per Capita (PPP)</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>0.06512696982096217</v>
+      </c>
+      <c r="D183" s="5" t="n">
+        <v>0.02927377044995029</v>
+      </c>
+      <c r="E183" s="5" t="n">
+        <v>0.02609768375030558</v>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>2.224755090305518</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.Pov</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>0.0003251763960326679</v>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>0.001182000910381517</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>0.7832342472491125</v>
+      </c>
+      <c r="F184" s="3" t="inlineStr"/>
+      <c r="G184" s="3" t="n">
+        <v>0.2751067221494016</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.Pov</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Earthquake Count (Log)</t>
         </is>
       </c>
-      <c r="C183" s="2" t="n">
-        <v>0.04680138000978051</v>
-      </c>
-      <c r="D183" s="2" t="n">
-        <v>0.01704152569431957</v>
-      </c>
-      <c r="E183" s="2" t="n">
-        <v>0.006026905606511769</v>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="C185" s="2" t="n">
+        <v>0.04680138000978103</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>0.01704152569431944</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>0.006026905606510841</v>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="G183" s="2" t="n">
-        <v>2.746313965619918</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.Pov</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C184" s="5" t="n">
-        <v>-0.007146346425070842</v>
-      </c>
-      <c r="D184" s="5" t="n">
-        <v>0.003298550144514929</v>
-      </c>
-      <c r="E184" s="5" t="n">
-        <v>0.03027213121352671</v>
-      </c>
-      <c r="F184" s="5" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="n">
-        <v>-2.166511379841932</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.Pov</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>Urban Population %</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="n">
-        <v>0.0003251763960326189</v>
-      </c>
-      <c r="D185" s="3" t="n">
-        <v>0.001182000910381524</v>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>0.7832342472491454</v>
-      </c>
-      <c r="F185" s="3" t="inlineStr"/>
-      <c r="G185" s="3" t="n">
-        <v>0.2751067221493587</v>
+      <c r="G185" s="2" t="n">
+        <v>2.746313965619969</v>
       </c>
     </row>
     <row r="186">
@@ -5220,13 +5220,13 @@
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>-0.004083627717762035</v>
+        <v>-0.004083627717761971</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>0.001239430815803851</v>
+        <v>0.001239430815803804</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.000985055890549406</v>
+        <v>0.0009850558905491558</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>-3.294760518854406</v>
+        <v>-3.294760518854478</v>
       </c>
     </row>
     <row r="187">
@@ -5249,13 +5249,13 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>0.001212690210663822</v>
+        <v>0.001212690210663894</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>0.0006963627221409395</v>
+        <v>0.0006963627221409429</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>0.08160237912643396</v>
+        <v>0.08160237912641753</v>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="G187" s="4" t="n">
-        <v>1.741463424313488</v>
+        <v>1.741463424313582</v>
       </c>
     </row>
     <row r="188">
@@ -5278,13 +5278,13 @@
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>0.003263072874734388</v>
+        <v>0.003263072874734436</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>0.001200869545717334</v>
+        <v>0.001200869545717333</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.006582519150402292</v>
+        <v>0.006582519150401499</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>2.717258411932836</v>
+        <v>2.717258411932876</v>
       </c>
     </row>
     <row r="189">
@@ -5364,13 +5364,13 @@
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>0.5688090981192709</v>
+        <v>0.5688090981192735</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>0.04129369192433389</v>
+        <v>0.04129369192433527</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>3.617764703159007e-43</v>
+        <v>3.617764703178902e-43</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>13.7747213100139</v>
+        <v>13.7747213100135</v>
       </c>
     </row>
     <row r="193">
@@ -5393,17 +5393,17 @@
         </is>
       </c>
       <c r="C193" s="3" t="n">
-        <v>-0.06978770717280246</v>
+        <v>-0.06978770717280539</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>0.05322908588930508</v>
+        <v>0.05322908588930723</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>0.1898299929023054</v>
+        <v>0.1898299929023048</v>
       </c>
       <c r="F193" s="3" t="inlineStr"/>
       <c r="G193" s="3" t="n">
-        <v>-1.311082202650119</v>
+        <v>-1.311082202650121</v>
       </c>
     </row>
     <row r="194">
@@ -5418,17 +5418,17 @@
         </is>
       </c>
       <c r="C194" s="3" t="n">
-        <v>0.08066282806283853</v>
+        <v>0.08066282806283805</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>0.05334708114504839</v>
+        <v>0.05334708114504891</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>0.1305241281444942</v>
+        <v>0.1305241281445003</v>
       </c>
       <c r="F194" s="3" t="inlineStr"/>
       <c r="G194" s="3" t="n">
-        <v>1.512038265852256</v>
+        <v>1.512038265852232</v>
       </c>
     </row>
     <row r="195">
@@ -5443,17 +5443,17 @@
         </is>
       </c>
       <c r="C195" s="3" t="n">
-        <v>0.06286890691488448</v>
+        <v>0.06286890691487873</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>0.07868759463497289</v>
+        <v>0.07868759463497481</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>0.4243086960975544</v>
+        <v>0.4243086960976079</v>
       </c>
       <c r="F195" s="3" t="inlineStr"/>
       <c r="G195" s="3" t="n">
-        <v>0.7989684677302645</v>
+        <v>0.798968467730172</v>
       </c>
     </row>
     <row r="196">
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>0.1945367234482893</v>
+        <v>0.1945367234482861</v>
       </c>
       <c r="D196" s="4" t="n">
         <v>0.1047601044299395</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>0.06331494384806755</v>
+        <v>0.06331494384807196</v>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="G196" s="4" t="n">
-        <v>1.856973363160302</v>
+        <v>1.856973363160271</v>
       </c>
     </row>
     <row r="197">
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="C197" s="5" t="n">
-        <v>-0.2209899535360883</v>
+        <v>-0.2209899535360877</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>0.106344666740236</v>
+        <v>0.1063446667402355</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>0.03770439147423188</v>
+        <v>0.03770439147423146</v>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>-2.078053938293793</v>
+        <v>-2.078053938293797</v>
       </c>
     </row>
     <row r="198">
@@ -5526,13 +5526,13 @@
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>-0.2087432261364673</v>
+        <v>-0.2087432261364704</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>0.0684635094854794</v>
+        <v>0.06846350948548027</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.0022962696875508</v>
+        <v>0.002296269687550744</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -5540,90 +5540,90 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>-3.04897057871011</v>
+        <v>-3.048970578710118</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="inlineStr">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.GDP</t>
         </is>
       </c>
-      <c r="B199" s="5" t="inlineStr">
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Poverty Gap ($4.20/day)</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>-0.006458140394471903</v>
+      </c>
+      <c r="D199" s="4" t="n">
+        <v>0.003319818102525944</v>
+      </c>
+      <c r="E199" s="4" t="n">
+        <v>0.05173532276603702</v>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="n">
+        <v>-1.945329591870744</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.GDP</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
         <is>
           <t>Poverty Gap Squared</t>
         </is>
       </c>
-      <c r="C199" s="5" t="n">
-        <v>0.0001417736846145625</v>
-      </c>
-      <c r="D199" s="5" t="n">
-        <v>6.299402323891567e-05</v>
-      </c>
-      <c r="E199" s="5" t="n">
-        <v>0.02441155173551372</v>
-      </c>
-      <c r="F199" s="5" t="inlineStr">
+      <c r="C200" s="5" t="n">
+        <v>0.000141773684614578</v>
+      </c>
+      <c r="D200" s="5" t="n">
+        <v>6.299402323891366e-05</v>
+      </c>
+      <c r="E200" s="5" t="n">
+        <v>0.02441155173549352</v>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="G199" s="5" t="n">
-        <v>2.250589457937325</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="3" t="inlineStr">
+      <c r="G200" s="5" t="n">
+        <v>2.250589457937644</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.GDP</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>Storm Count (Log)</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="n">
-        <v>0.005796596808573914</v>
-      </c>
-      <c r="D200" s="3" t="n">
-        <v>0.01660763266553399</v>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>0.7270652152220882</v>
-      </c>
-      <c r="F200" s="3" t="inlineStr"/>
-      <c r="G200" s="3" t="n">
-        <v>0.3490320941770141</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.GDP</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>Log GDP per Capita (PPP)</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="n">
-        <v>0.07628993504846308</v>
-      </c>
-      <c r="D201" s="2" t="n">
-        <v>0.02837589308621943</v>
-      </c>
-      <c r="E201" s="2" t="n">
-        <v>0.007176363527825531</v>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="n">
-        <v>2.6885474517633</v>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Flood Count (Log)</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>-0.02596815348505133</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0.01710927971774595</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>0.1290694129359767</v>
+      </c>
+      <c r="F201" s="3" t="inlineStr"/>
+      <c r="G201" s="3" t="n">
+        <v>-1.517781806917146</v>
       </c>
     </row>
     <row r="202">
@@ -5634,21 +5634,21 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Flood Count (Log)</t>
+          <t>Storm Count (Log)</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
-        <v>-0.02596815348505114</v>
+        <v>0.005796596808574072</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>0.01710927971774596</v>
+        <v>0.01660763266553398</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>0.1290694129359796</v>
+        <v>0.7270652152220809</v>
       </c>
       <c r="F202" s="3" t="inlineStr"/>
       <c r="G202" s="3" t="n">
-        <v>-1.517781806917134</v>
+        <v>0.3490320941770238</v>
       </c>
     </row>
     <row r="203">
@@ -5659,79 +5659,79 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
+          <t>Log GDP per Capita (PPP)</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>0.07628993504846328</v>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>0.02837589308621951</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>0.007176363527825551</v>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>2.688547451763299</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.GDP</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>0.0002176305618392569</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>0.001160402919084613</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>0.8512314554058291</v>
+      </c>
+      <c r="F204" s="3" t="inlineStr"/>
+      <c r="G204" s="3" t="n">
+        <v>0.1875474098349696</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.GDP</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
           <t>Earthquake Count (Log)</t>
         </is>
       </c>
-      <c r="C203" s="2" t="n">
-        <v>0.0537982656780885</v>
-      </c>
-      <c r="D203" s="2" t="n">
-        <v>0.01810771158413113</v>
-      </c>
-      <c r="E203" s="2" t="n">
-        <v>0.002968181933770229</v>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="C205" s="2" t="n">
+        <v>0.05379826567808888</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>0.01810771158413112</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>0.002968181933770006</v>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="G203" s="2" t="n">
-        <v>2.971014058189171</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.GDP</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="n">
-        <v>-0.006458140394471892</v>
-      </c>
-      <c r="D204" s="4" t="n">
-        <v>0.003319818102525935</v>
-      </c>
-      <c r="E204" s="4" t="n">
-        <v>0.05173532276603678</v>
-      </c>
-      <c r="F204" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G204" s="4" t="n">
-        <v>-1.945329591870746</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.GDP</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>Urban Population %</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="n">
-        <v>0.0002176305618392458</v>
-      </c>
-      <c r="D205" s="3" t="n">
-        <v>0.001160402919084612</v>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>0.8512314554058366</v>
-      </c>
-      <c r="F205" s="3" t="inlineStr"/>
-      <c r="G205" s="3" t="n">
-        <v>0.1875474098349602</v>
+      <c r="G205" s="2" t="n">
+        <v>2.971014058189194</v>
       </c>
     </row>
     <row r="206">
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="C206" s="5" t="n">
-        <v>0.03515262494560402</v>
+        <v>0.03515262494560409</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>0.01690098237789889</v>
+        <v>0.01690098237789879</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>0.03753323124461905</v>
+        <v>0.03753323124461758</v>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>2.079916075859145</v>
+        <v>2.079916075859161</v>
       </c>
     </row>
     <row r="207">
@@ -5775,13 +5775,13 @@
         </is>
       </c>
       <c r="C207" s="5" t="n">
-        <v>-0.02379819340057953</v>
+        <v>-0.02379819340057952</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>0.01022753667298308</v>
+        <v>0.01022753667298311</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>0.01997195035886508</v>
+        <v>0.01997195035886549</v>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>-2.32687441380137</v>
+        <v>-2.326874413801363</v>
       </c>
     </row>
     <row r="208">
@@ -5804,17 +5804,17 @@
         </is>
       </c>
       <c r="C208" s="3" t="n">
-        <v>0.0009465498009257507</v>
+        <v>0.0009465498009256349</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>0.01633468650842023</v>
+        <v>0.0163346865084203</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>0.9537906639152105</v>
+        <v>0.9537906639152164</v>
       </c>
       <c r="F208" s="3" t="inlineStr"/>
       <c r="G208" s="3" t="n">
-        <v>0.05794722784779625</v>
+        <v>0.05794722784778892</v>
       </c>
     </row>
     <row r="209">
@@ -5886,13 +5886,13 @@
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>0.5483937414539864</v>
+        <v>0.5483937414539881</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>0.03954218528489617</v>
+        <v>0.03954218528489731</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>9.820922301941226e-44</v>
+        <v>9.820922301990464e-44</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>13.8685744731325</v>
+        <v>13.86857447313214</v>
       </c>
     </row>
     <row r="213">
@@ -5915,17 +5915,17 @@
         </is>
       </c>
       <c r="C213" s="3" t="n">
-        <v>-0.04251136444518731</v>
+        <v>-0.04251136444518644</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>0.05561244005547577</v>
+        <v>0.05561244005547471</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>0.4446158904277681</v>
+        <v>0.4446158904277688</v>
       </c>
       <c r="F213" s="3" t="inlineStr"/>
       <c r="G213" s="3" t="n">
-        <v>-0.7644218524269106</v>
+        <v>-0.7644218524269094</v>
       </c>
     </row>
     <row r="214">
@@ -5940,13 +5940,13 @@
         </is>
       </c>
       <c r="C214" s="5" t="n">
-        <v>0.1164082234862002</v>
+        <v>0.1164082234862013</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>0.05592532775542652</v>
+        <v>0.05592532775542538</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>0.03738873019018257</v>
+        <v>0.03738873019017699</v>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>2.081493808946072</v>
+        <v>2.081493808946133</v>
       </c>
     </row>
     <row r="215">
@@ -5969,17 +5969,17 @@
         </is>
       </c>
       <c r="C215" s="3" t="n">
-        <v>0.1103240322399426</v>
+        <v>0.1103240322399449</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>0.0822750919519817</v>
+        <v>0.08227509195197992</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>0.1799475490435484</v>
+        <v>0.1799475490435299</v>
       </c>
       <c r="F215" s="3" t="inlineStr"/>
       <c r="G215" s="3" t="n">
-        <v>1.340916547432498</v>
+        <v>1.340916547432555</v>
       </c>
     </row>
     <row r="216">
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="C216" s="5" t="n">
-        <v>0.2044838431619672</v>
+        <v>0.2044838431619695</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>0.09878560071961145</v>
+        <v>0.0987856007196103</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0.03845457253772081</v>
+        <v>0.03845457253771632</v>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>2.069976207791303</v>
+        <v>2.069976207791351</v>
       </c>
     </row>
     <row r="217">
@@ -6026,10 +6026,10 @@
         <v>-0.2282655091658433</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>0.09437011937474961</v>
+        <v>0.09437011937474962</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>0.01557040930207336</v>
+        <v>0.01557040930207339</v>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>-0.1903502483616155</v>
+        <v>-0.1903502483616172</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>0.06481045741601946</v>
+        <v>0.06481045741602089</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>0.003313722004421453</v>
+        <v>0.00331372200442187</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>-2.937029855224659</v>
+        <v>-2.93702985522462</v>
       </c>
     </row>
     <row r="219">
@@ -6077,75 +6077,83 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
+          <t>Poverty Gap ($4.20/day)</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="n">
+        <v>-0.007259937441993879</v>
+      </c>
+      <c r="D219" s="5" t="n">
+        <v>0.003321719898023638</v>
+      </c>
+      <c r="E219" s="5" t="n">
+        <v>0.02884518170619365</v>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>-2.185595915631962</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.WGI</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Government Effectiveness (WGI)</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="n">
+        <v>0.05177711522805485</v>
+      </c>
+      <c r="D220" s="4" t="n">
+        <v>0.02848014907165398</v>
+      </c>
+      <c r="E220" s="4" t="n">
+        <v>0.06906303684183158</v>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="n">
+        <v>1.818007170460639</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.WGI</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
           <t>Poverty Gap Squared</t>
         </is>
       </c>
-      <c r="C219" s="5" t="n">
-        <v>0.0001504859333628415</v>
-      </c>
-      <c r="D219" s="5" t="n">
-        <v>6.212905450099896e-05</v>
-      </c>
-      <c r="E219" s="5" t="n">
-        <v>0.01542895033841705</v>
-      </c>
-      <c r="F219" s="5" t="inlineStr">
+      <c r="C221" s="5" t="n">
+        <v>0.0001504859333628719</v>
+      </c>
+      <c r="D221" s="5" t="n">
+        <v>6.212905450099294e-05</v>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>0.01542895033838631</v>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="G219" s="5" t="n">
-        <v>2.422150708255538</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.WGI</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>Storm Count (Log)</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="n">
-        <v>0.004206956567847178</v>
-      </c>
-      <c r="D220" s="3" t="n">
-        <v>0.01590118135683668</v>
-      </c>
-      <c r="E220" s="3" t="n">
-        <v>0.7913416531197733</v>
-      </c>
-      <c r="F220" s="3" t="inlineStr"/>
-      <c r="G220" s="3" t="n">
-        <v>0.2645688061433503</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.WGI</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>Log GDP per Capita (PPP)</t>
-        </is>
-      </c>
-      <c r="C221" s="3" t="n">
-        <v>0.03491588077392171</v>
-      </c>
-      <c r="D221" s="3" t="n">
-        <v>0.03566409925465602</v>
-      </c>
-      <c r="E221" s="3" t="n">
-        <v>0.3275698991360604</v>
-      </c>
-      <c r="F221" s="3" t="inlineStr"/>
-      <c r="G221" s="3" t="n">
-        <v>0.9790204015698889</v>
+      <c r="G221" s="5" t="n">
+        <v>2.422150708256262</v>
       </c>
     </row>
     <row r="222">
@@ -6160,75 +6168,67 @@
         </is>
       </c>
       <c r="C222" s="3" t="n">
-        <v>-0.02055196266261291</v>
+        <v>-0.02055196266261295</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>0.01848421937428348</v>
+        <v>0.01848421937428355</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>0.2661960576465329</v>
+        <v>0.2661960576465338</v>
       </c>
       <c r="F222" s="3" t="inlineStr"/>
       <c r="G222" s="3" t="n">
-        <v>-1.111865329363393</v>
+        <v>-1.111865329363391</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+      <c r="A223" s="3" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.WGI</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>Earthquake Count (Log)</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="n">
-        <v>0.05567882975984961</v>
-      </c>
-      <c r="D223" s="2" t="n">
-        <v>0.01824933209308747</v>
-      </c>
-      <c r="E223" s="2" t="n">
-        <v>0.00228075681973876</v>
-      </c>
-      <c r="F223" s="2" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="n">
-        <v>3.051006440994068</v>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Storm Count (Log)</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>0.004206956567847153</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>0.01590118135683663</v>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>0.7913416531197739</v>
+      </c>
+      <c r="F223" s="3" t="inlineStr"/>
+      <c r="G223" s="3" t="n">
+        <v>0.2645688061433495</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="inlineStr">
+      <c r="A224" s="3" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.WGI</t>
         </is>
       </c>
-      <c r="B224" s="5" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C224" s="5" t="n">
-        <v>-0.007259937441994226</v>
-      </c>
-      <c r="D224" s="5" t="n">
-        <v>0.003321719898023614</v>
-      </c>
-      <c r="E224" s="5" t="n">
-        <v>0.02884518170618485</v>
-      </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="n">
-        <v>-2.185595915632082</v>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>Log GDP per Capita (PPP)</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>0.03491588077392128</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>0.03566409925465623</v>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>0.3275698991360692</v>
+      </c>
+      <c r="F224" s="3" t="inlineStr"/>
+      <c r="G224" s="3" t="n">
+        <v>0.9790204015698711</v>
       </c>
     </row>
     <row r="225">
@@ -6243,46 +6243,46 @@
         </is>
       </c>
       <c r="C225" s="3" t="n">
-        <v>0.0003024778670397604</v>
+        <v>0.0003024778670397805</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>0.001143296439908442</v>
+        <v>0.001143296439908443</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>0.7913434774003802</v>
+        <v>0.7913434774003668</v>
       </c>
       <c r="F225" s="3" t="inlineStr"/>
       <c r="G225" s="3" t="n">
-        <v>0.2645664383105955</v>
+        <v>0.264566438310613</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="4" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.WGI</t>
         </is>
       </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>Government Effectiveness (WGI)</t>
-        </is>
-      </c>
-      <c r="C226" s="4" t="n">
-        <v>0.05177711522805451</v>
-      </c>
-      <c r="D226" s="4" t="n">
-        <v>0.02848014907165414</v>
-      </c>
-      <c r="E226" s="4" t="n">
-        <v>0.06906303684183497</v>
-      </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G226" s="4" t="n">
-        <v>1.818007170460617</v>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Earthquake Count (Log)</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>0.05567882975984982</v>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>0.01824933209308744</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>0.002280756819738641</v>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="n">
+        <v>3.051006440994083</v>
       </c>
     </row>
     <row r="227">
@@ -6297,13 +6297,13 @@
         </is>
       </c>
       <c r="C227" s="5" t="n">
-        <v>0.03489288454154203</v>
+        <v>0.03489288454154196</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>0.01716547663678548</v>
+        <v>0.01716547663678528</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>0.04207918903078043</v>
+        <v>0.04207918903077849</v>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>2.032736129608359</v>
+        <v>2.032736129608379</v>
       </c>
     </row>
     <row r="228">
@@ -6326,13 +6326,13 @@
         </is>
       </c>
       <c r="C228" s="5" t="n">
-        <v>-0.03115589146864382</v>
+        <v>-0.031155891468644</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>0.01468979585683547</v>
+        <v>0.01468979585683539</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>0.03392848004784106</v>
+        <v>0.03392848004783917</v>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>-2.120920656235419</v>
+        <v>-2.120920656235442</v>
       </c>
     </row>
     <row r="229">
@@ -6355,17 +6355,17 @@
         </is>
       </c>
       <c r="C229" s="3" t="n">
-        <v>0.005449826673728811</v>
+        <v>0.00544982667372888</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>0.01721904756366976</v>
+        <v>0.01721904756366979</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>0.7516231080354584</v>
+        <v>0.7516231080354558</v>
       </c>
       <c r="F229" s="3" t="inlineStr"/>
       <c r="G229" s="3" t="n">
-        <v>0.3164998908085559</v>
+        <v>0.3164998908085594</v>
       </c>
     </row>
     <row r="230">
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>0.5545078305150786</v>
+        <v>0.5545078305150749</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>0.04405273481073428</v>
+        <v>0.04405273481073217</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>2.478097324348293e-36</v>
+        <v>2.478097324331957e-36</v>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>12.58736450523299</v>
+        <v>12.58736450523351</v>
       </c>
     </row>
     <row r="234">
@@ -6466,17 +6466,17 @@
         </is>
       </c>
       <c r="C234" s="3" t="n">
-        <v>-0.07590595700976152</v>
+        <v>-0.07590595700976391</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>0.05119076941600663</v>
+        <v>0.05119076941600745</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>0.1381260810262533</v>
+        <v>0.1381260810262472</v>
       </c>
       <c r="F234" s="3" t="inlineStr"/>
       <c r="G234" s="3" t="n">
-        <v>-1.482805550213645</v>
+        <v>-1.482805550213667</v>
       </c>
     </row>
     <row r="235">
@@ -6491,13 +6491,13 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>0.1099453921841067</v>
+        <v>0.1099453921841066</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>0.06350926510058678</v>
+        <v>0.06350926510058699</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>0.08342128630042787</v>
+        <v>0.08342128630042903</v>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G235" s="4" t="n">
-        <v>1.731170908842572</v>
+        <v>1.731170908842565</v>
       </c>
     </row>
     <row r="236">
@@ -6520,17 +6520,17 @@
         </is>
       </c>
       <c r="C236" s="3" t="n">
-        <v>0.06297553848237854</v>
+        <v>0.06297553848238005</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>0.08520515645958933</v>
+        <v>0.0852051564595892</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>0.4598433740859232</v>
+        <v>0.4598433740859118</v>
       </c>
       <c r="F236" s="3" t="inlineStr"/>
       <c r="G236" s="3" t="n">
-        <v>0.7391047807329156</v>
+        <v>0.7391047807329344</v>
       </c>
     </row>
     <row r="237">
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>0.1471247208876012</v>
+        <v>0.1471247208875992</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>0.07810624030462554</v>
+        <v>0.07810624030462437</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>0.05961250481262775</v>
+        <v>0.05961250481262739</v>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="G237" s="4" t="n">
-        <v>1.883648736820435</v>
+        <v>1.883648736820437</v>
       </c>
     </row>
     <row r="238">
@@ -6574,13 +6574,13 @@
         </is>
       </c>
       <c r="C238" s="5" t="n">
-        <v>-0.202885661285111</v>
+        <v>-0.2028856612851078</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>0.09413965573894292</v>
+        <v>0.09413965573894267</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.03114961430704403</v>
+        <v>0.03114961430704617</v>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>-2.155156184634133</v>
+        <v>-2.155156184634105</v>
       </c>
     </row>
     <row r="239">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>-0.2137013879849435</v>
+        <v>-0.2137013879849473</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>0.06738455433678185</v>
+        <v>0.06738455433678169</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>0.001517214969809327</v>
+        <v>0.001517214969808985</v>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
@@ -6617,198 +6617,198 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>-3.171370503051537</v>
+        <v>-3.171370503051602</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
+      <c r="A240" s="3" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.BQCI</t>
         </is>
       </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Poverty Gap ($4.20/day)</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>-0.005563706077729014</v>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>0.00351995430839188</v>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>0.1139652166189933</v>
+      </c>
+      <c r="F240" s="3" t="inlineStr"/>
+      <c r="G240" s="3" t="n">
+        <v>-1.580618834870853</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.BQCI</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>Poverty Gap Squared</t>
         </is>
       </c>
-      <c r="C240" s="5" t="n">
-        <v>0.000143824343229957</v>
-      </c>
-      <c r="D240" s="5" t="n">
-        <v>6.492964573080489e-05</v>
-      </c>
-      <c r="E240" s="5" t="n">
-        <v>0.02675459131135941</v>
-      </c>
-      <c r="F240" s="5" t="inlineStr">
+      <c r="C241" s="5" t="n">
+        <v>0.0001438243432299822</v>
+      </c>
+      <c r="D241" s="5" t="n">
+        <v>6.492964573080452e-05</v>
+      </c>
+      <c r="E241" s="5" t="n">
+        <v>0.02675459131133185</v>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="G240" s="5" t="n">
-        <v>2.215079746873186</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="3" t="inlineStr">
+      <c r="G241" s="5" t="n">
+        <v>2.215079746873588</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.BQCI</t>
         </is>
       </c>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>Building Quality Index</t>
-        </is>
-      </c>
-      <c r="C241" s="3" t="n">
-        <v>0.01006850775024001</v>
-      </c>
-      <c r="D241" s="3" t="n">
-        <v>0.006380816106893239</v>
-      </c>
-      <c r="E241" s="3" t="n">
-        <v>0.1145807345989341</v>
-      </c>
-      <c r="F241" s="3" t="inlineStr"/>
-      <c r="G241" s="3" t="n">
-        <v>1.577934167286679</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="3" t="inlineStr">
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Flood Count (Log)</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="n">
+        <v>-0.03302134526075502</v>
+      </c>
+      <c r="D242" s="4" t="n">
+        <v>0.01957465461031466</v>
+      </c>
+      <c r="E242" s="4" t="n">
+        <v>0.09161412914076637</v>
+      </c>
+      <c r="F242" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G242" s="4" t="n">
+        <v>-1.686943954727803</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.BQCI</t>
         </is>
       </c>
-      <c r="B242" s="3" t="inlineStr">
+      <c r="B243" s="3" t="inlineStr">
         <is>
           <t>Storm Count (Log)</t>
         </is>
       </c>
-      <c r="C242" s="3" t="n">
-        <v>0.004340459215987902</v>
-      </c>
-      <c r="D242" s="3" t="n">
-        <v>0.0171676956802097</v>
-      </c>
-      <c r="E242" s="3" t="n">
-        <v>0.8004018024440515</v>
-      </c>
-      <c r="F242" s="3" t="inlineStr"/>
-      <c r="G242" s="3" t="n">
-        <v>0.252827129327055</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="5" t="inlineStr">
+      <c r="C243" s="3" t="n">
+        <v>0.004340459215987567</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>0.01716769568020977</v>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>0.8004018024440673</v>
+      </c>
+      <c r="F243" s="3" t="inlineStr"/>
+      <c r="G243" s="3" t="n">
+        <v>0.2528271293270345</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.BQCI</t>
         </is>
       </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>Log GDP per Capita (PPP)</t>
         </is>
       </c>
-      <c r="C243" s="5" t="n">
-        <v>0.06326101233577061</v>
-      </c>
-      <c r="D243" s="5" t="n">
-        <v>0.02959626358730461</v>
-      </c>
-      <c r="E243" s="5" t="n">
-        <v>0.03256009401271968</v>
-      </c>
-      <c r="F243" s="5" t="inlineStr">
+      <c r="C244" s="5" t="n">
+        <v>0.06326101233577075</v>
+      </c>
+      <c r="D244" s="5" t="n">
+        <v>0.02959626358730451</v>
+      </c>
+      <c r="E244" s="5" t="n">
+        <v>0.03256009401271875</v>
+      </c>
+      <c r="F244" s="5" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="G243" s="5" t="n">
-        <v>2.137466175389335</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="4" t="inlineStr">
+      <c r="G244" s="5" t="n">
+        <v>2.137466175389346</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
         <is>
           <t>VULN-J+K+N.Int.BQCI</t>
         </is>
       </c>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>Flood Count (Log)</t>
-        </is>
-      </c>
-      <c r="C244" s="4" t="n">
-        <v>-0.03302134526075558</v>
-      </c>
-      <c r="D244" s="4" t="n">
-        <v>0.01957465461031465</v>
-      </c>
-      <c r="E244" s="4" t="n">
-        <v>0.09161412914076084</v>
-      </c>
-      <c r="F244" s="4" t="inlineStr">
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>0.0007775475273128755</v>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>0.001216254031049666</v>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>0.5226297536126658</v>
+      </c>
+      <c r="F245" s="3" t="inlineStr"/>
+      <c r="G245" s="3" t="n">
+        <v>0.6392969786433736</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>VULN-J+K+N.Int.BQCI</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Earthquake Count (Log)</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="n">
+        <v>0.04336389269239597</v>
+      </c>
+      <c r="D246" s="4" t="n">
+        <v>0.02530176573371342</v>
+      </c>
+      <c r="E246" s="4" t="n">
+        <v>0.08655292725591496</v>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
-        <v>-1.686943954727832</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.BQCI</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>Earthquake Count (Log)</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="n">
-        <v>0.04336389269239598</v>
-      </c>
-      <c r="D245" s="4" t="n">
-        <v>0.02530176573371344</v>
-      </c>
-      <c r="E245" s="4" t="n">
-        <v>0.08655292725591508</v>
-      </c>
-      <c r="F245" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G245" s="4" t="n">
+      <c r="G246" s="4" t="n">
         <v>1.713868239425504</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="3" t="inlineStr">
-        <is>
-          <t>VULN-J+K+N.Int.BQCI</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="n">
-        <v>-0.005563706077728457</v>
-      </c>
-      <c r="D246" s="3" t="n">
-        <v>0.003519954308391914</v>
-      </c>
-      <c r="E246" s="3" t="n">
-        <v>0.1139652166190329</v>
-      </c>
-      <c r="F246" s="3" t="inlineStr"/>
-      <c r="G246" s="3" t="n">
-        <v>-1.58061883487068</v>
       </c>
     </row>
     <row r="247">
@@ -6819,21 +6819,21 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Urban Population %</t>
+          <t>Building Quality Index</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
-        <v>0.0007775475273128302</v>
+        <v>0.01006850775024009</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>0.001216254031049659</v>
+        <v>0.006380816106893224</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>0.5226297536126876</v>
+        <v>0.1145807345989303</v>
       </c>
       <c r="F247" s="3" t="inlineStr"/>
       <c r="G247" s="3" t="n">
-        <v>0.6392969786433403</v>
+        <v>1.577934167286696</v>
       </c>
     </row>
     <row r="248">
@@ -6848,17 +6848,17 @@
         </is>
       </c>
       <c r="C248" s="3" t="n">
-        <v>0.003052281911642688</v>
+        <v>0.003052281911642576</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>0.007579434204578417</v>
+        <v>0.007579434204578406</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>0.6871646863538527</v>
+        <v>0.6871646863538633</v>
       </c>
       <c r="F248" s="3" t="inlineStr"/>
       <c r="G248" s="3" t="n">
-        <v>0.4027057731827705</v>
+        <v>0.4027057731827562</v>
       </c>
     </row>
     <row r="249">
@@ -6873,17 +6873,17 @@
         </is>
       </c>
       <c r="C249" s="3" t="n">
-        <v>-0.00632925753182289</v>
+        <v>-0.006329257531822998</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>0.004998006873703664</v>
+        <v>0.004998006873703676</v>
       </c>
       <c r="E249" s="3" t="n">
-        <v>0.2053855460154549</v>
+        <v>0.2053855460154481</v>
       </c>
       <c r="F249" s="3" t="inlineStr"/>
       <c r="G249" s="3" t="n">
-        <v>-1.266356307976169</v>
+        <v>-1.266356307976188</v>
       </c>
     </row>
     <row r="250">
@@ -6898,17 +6898,17 @@
         </is>
       </c>
       <c r="C250" s="3" t="n">
-        <v>0.008689253209344657</v>
+        <v>0.008689253209344638</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>0.005819734140077075</v>
+        <v>0.00581973414007713</v>
       </c>
       <c r="E250" s="3" t="n">
-        <v>0.1354196399435105</v>
+        <v>0.1354196399435151</v>
       </c>
       <c r="F250" s="3" t="inlineStr"/>
       <c r="G250" s="3" t="n">
-        <v>1.493067037118912</v>
+        <v>1.493067037118895</v>
       </c>
     </row>
     <row r="251">
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="C251" s="3" t="n">
-        <v>0.6821034929101074</v>
+        <v>0.6821034929101073</v>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr"/>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="C252" s="3" t="n">
-        <v>0.6411622760879243</v>
+        <v>0.6411622760879241</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr"/>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>0.5964875769491026</v>
+        <v>0.5964875769491037</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>0.04282809721912378</v>
+        <v>0.04282809721912438</v>
       </c>
       <c r="E329" s="2" t="n">
-        <v>4.312910690442407e-44</v>
+        <v>4.31291069045257e-44</v>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="G329" s="2" t="n">
-        <v>13.92748255653899</v>
+        <v>13.92748255653882</v>
       </c>
     </row>
     <row r="330">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="C330" s="4" t="n">
-        <v>-0.1051427662294171</v>
+        <v>-0.1051427662294162</v>
       </c>
       <c r="D330" s="4" t="n">
-        <v>0.05411501059695731</v>
+        <v>0.05411501059695706</v>
       </c>
       <c r="E330" s="4" t="n">
-        <v>0.05202218556811604</v>
+        <v>0.05202218556811681</v>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="G330" s="4" t="n">
-        <v>-1.942950118082928</v>
+        <v>-1.942950118082921</v>
       </c>
     </row>
     <row r="331">
@@ -8959,17 +8959,17 @@
         </is>
       </c>
       <c r="C331" s="3" t="n">
-        <v>0.06216564835794316</v>
+        <v>0.06216564835794336</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>0.05856080223898608</v>
+        <v>0.05856080223898637</v>
       </c>
       <c r="E331" s="3" t="n">
-        <v>0.2884366974560426</v>
+        <v>0.2884366974560434</v>
       </c>
       <c r="F331" s="3" t="inlineStr"/>
       <c r="G331" s="3" t="n">
-        <v>1.061557321299079</v>
+        <v>1.061557321299077</v>
       </c>
     </row>
     <row r="332">
@@ -8984,17 +8984,17 @@
         </is>
       </c>
       <c r="C332" s="3" t="n">
-        <v>0.04937505060234983</v>
+        <v>0.04937505060234968</v>
       </c>
       <c r="D332" s="3" t="n">
-        <v>0.0763572083819762</v>
+        <v>0.07635720838197586</v>
       </c>
       <c r="E332" s="3" t="n">
-        <v>0.5178698352193547</v>
+        <v>0.517869835219354</v>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
       <c r="G332" s="3" t="n">
-        <v>0.646632474505244</v>
+        <v>0.6466324745052449</v>
       </c>
     </row>
     <row r="333">
@@ -9009,17 +9009,17 @@
         </is>
       </c>
       <c r="C333" s="3" t="n">
-        <v>0.1056308012701142</v>
+        <v>0.1056308012701167</v>
       </c>
       <c r="D333" s="3" t="n">
-        <v>0.06907564277967464</v>
+        <v>0.06907564277967389</v>
       </c>
       <c r="E333" s="3" t="n">
-        <v>0.1262136926292317</v>
+        <v>0.1262136926292188</v>
       </c>
       <c r="F333" s="3" t="inlineStr"/>
       <c r="G333" s="3" t="n">
-        <v>1.529204753215787</v>
+        <v>1.529204753215839</v>
       </c>
     </row>
     <row r="334">
@@ -9034,13 +9034,13 @@
         </is>
       </c>
       <c r="C334" s="5" t="n">
-        <v>-0.2552088875792644</v>
+        <v>-0.2552088875792635</v>
       </c>
       <c r="D334" s="5" t="n">
-        <v>0.1088655808668449</v>
+        <v>0.108865580866845</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>0.01906503520263009</v>
+        <v>0.01906503520263053</v>
       </c>
       <c r="F334" s="5" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>-2.344256885850947</v>
+        <v>-2.344256885850938</v>
       </c>
     </row>
     <row r="335">
@@ -9063,13 +9063,13 @@
         </is>
       </c>
       <c r="C335" s="2" t="n">
-        <v>-0.2675962070608258</v>
+        <v>-0.2675962070608242</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>0.05546253637162173</v>
+        <v>0.05546253637162095</v>
       </c>
       <c r="E335" s="2" t="n">
-        <v>1.401367064829056e-06</v>
+        <v>1.401367064828782e-06</v>
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
@@ -9077,32 +9077,36 @@
         </is>
       </c>
       <c r="G335" s="2" t="n">
-        <v>-4.824810125303709</v>
+        <v>-4.824810125303748</v>
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="3" t="inlineStr">
+      <c r="A336" s="5" t="inlineStr">
         <is>
           <t>VULN-M.Int.Pov</t>
         </is>
       </c>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>3 Hazards Combined (Log)</t>
-        </is>
-      </c>
-      <c r="C336" s="3" t="n">
-        <v>0.01954197351930471</v>
-      </c>
-      <c r="D336" s="3" t="n">
-        <v>0.01756075653019982</v>
-      </c>
-      <c r="E336" s="3" t="n">
-        <v>0.2657854397211986</v>
-      </c>
-      <c r="F336" s="3" t="inlineStr"/>
-      <c r="G336" s="3" t="n">
-        <v>1.112820708247833</v>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>Poverty Gap ($4.20/day)</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="n">
+        <v>-0.007256240206297284</v>
+      </c>
+      <c r="D336" s="5" t="n">
+        <v>0.003127574574340307</v>
+      </c>
+      <c r="E336" s="5" t="n">
+        <v>0.02033625626835887</v>
+      </c>
+      <c r="F336" s="5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="G336" s="5" t="n">
+        <v>-2.320085431640852</v>
       </c>
     </row>
     <row r="337">
@@ -9117,13 +9121,13 @@
         </is>
       </c>
       <c r="C337" s="5" t="n">
-        <v>0.0001185583856504741</v>
+        <v>0.0001185583856504391</v>
       </c>
       <c r="D337" s="5" t="n">
-        <v>6.032367914558334e-05</v>
+        <v>6.032367914558651e-05</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>0.04937135936284581</v>
+        <v>0.04937135936292478</v>
       </c>
       <c r="F337" s="5" t="inlineStr">
         <is>
@@ -9131,7 +9135,7 @@
         </is>
       </c>
       <c r="G337" s="5" t="n">
-        <v>1.965370602882971</v>
+        <v>1.965370602882288</v>
       </c>
     </row>
     <row r="338">
@@ -9146,13 +9150,13 @@
         </is>
       </c>
       <c r="C338" s="5" t="n">
-        <v>0.06649691467238442</v>
+        <v>0.06649691467238435</v>
       </c>
       <c r="D338" s="5" t="n">
-        <v>0.02742948563197729</v>
+        <v>0.02742948563197735</v>
       </c>
       <c r="E338" s="5" t="n">
-        <v>0.01533852560851047</v>
+        <v>0.01533852560851077</v>
       </c>
       <c r="F338" s="5" t="inlineStr">
         <is>
@@ -9160,36 +9164,32 @@
         </is>
       </c>
       <c r="G338" s="5" t="n">
-        <v>2.424285878509596</v>
+        <v>2.424285878509589</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="5" t="inlineStr">
+      <c r="A339" s="3" t="inlineStr">
         <is>
           <t>VULN-M.Int.Pov</t>
         </is>
       </c>
-      <c r="B339" s="5" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C339" s="5" t="n">
-        <v>-0.007256240206297451</v>
-      </c>
-      <c r="D339" s="5" t="n">
-        <v>0.003127574574340308</v>
-      </c>
-      <c r="E339" s="5" t="n">
-        <v>0.02033625626835602</v>
-      </c>
-      <c r="F339" s="5" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G339" s="5" t="n">
-        <v>-2.320085431640905</v>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="n">
+        <v>0.0001978937415189373</v>
+      </c>
+      <c r="D339" s="3" t="n">
+        <v>0.001158551554222977</v>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>0.86437211339202</v>
+      </c>
+      <c r="F339" s="3" t="inlineStr"/>
+      <c r="G339" s="3" t="n">
+        <v>0.1708113383453717</v>
       </c>
     </row>
     <row r="340">
@@ -9200,21 +9200,21 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Urban Population %</t>
+          <t>3 Hazards Combined (Log)</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
-        <v>0.0001978937415189128</v>
+        <v>0.01954197351930387</v>
       </c>
       <c r="D340" s="3" t="n">
-        <v>0.001158551554222981</v>
+        <v>0.01756075653019996</v>
       </c>
       <c r="E340" s="3" t="n">
-        <v>0.8643721133920371</v>
+        <v>0.2657854397212233</v>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
       <c r="G340" s="3" t="n">
-        <v>0.1708113383453501</v>
+        <v>1.112820708247775</v>
       </c>
     </row>
     <row r="341">
@@ -9229,13 +9229,13 @@
         </is>
       </c>
       <c r="C341" s="5" t="n">
-        <v>0.00264732496281249</v>
+        <v>0.002647324962812533</v>
       </c>
       <c r="D341" s="5" t="n">
-        <v>0.001168843970498314</v>
+        <v>0.001168843970498344</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>0.02351827831740642</v>
+        <v>0.02351827831740762</v>
       </c>
       <c r="F341" s="5" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="G341" s="5" t="n">
-        <v>2.264908772796983</v>
+        <v>2.264908772796963</v>
       </c>
     </row>
     <row r="342">
@@ -9258,7 +9258,7 @@
         </is>
       </c>
       <c r="C342" s="3" t="n">
-        <v>0.6468034760938564</v>
+        <v>0.6468034760938566</v>
       </c>
       <c r="D342" s="3" t="inlineStr"/>
       <c r="E342" s="3" t="inlineStr"/>
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>0.6158665542918584</v>
+        <v>0.6158665542918587</v>
       </c>
       <c r="D343" s="3" t="inlineStr"/>
       <c r="E343" s="3" t="inlineStr"/>
@@ -9315,13 +9315,13 @@
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>0.5882384798204409</v>
+        <v>0.5882384798204394</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>0.04401155610989737</v>
+        <v>0.04401155610989659</v>
       </c>
       <c r="E345" s="2" t="n">
-        <v>9.612698832017787e-41</v>
+        <v>9.612698831991137e-41</v>
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="G345" s="2" t="n">
-        <v>13.36554604776079</v>
+        <v>13.36554604776099</v>
       </c>
     </row>
     <row r="346">
@@ -9344,13 +9344,13 @@
         </is>
       </c>
       <c r="C346" s="4" t="n">
-        <v>-0.1003835267337857</v>
+        <v>-0.1003835267337863</v>
       </c>
       <c r="D346" s="4" t="n">
-        <v>0.05352010213939642</v>
+        <v>0.05352010213939656</v>
       </c>
       <c r="E346" s="4" t="n">
-        <v>0.06070708590503501</v>
+        <v>0.06070708590503412</v>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="G346" s="4" t="n">
-        <v>-1.875622854237659</v>
+        <v>-1.875622854237665</v>
       </c>
     </row>
     <row r="347">
@@ -9373,17 +9373,17 @@
         </is>
       </c>
       <c r="C347" s="3" t="n">
-        <v>0.06617430185394499</v>
+        <v>0.06617430185394425</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>0.06116893912179459</v>
+        <v>0.06116893912179472</v>
       </c>
       <c r="E347" s="3" t="n">
-        <v>0.279328738799986</v>
+        <v>0.2793287387999924</v>
       </c>
       <c r="F347" s="3" t="inlineStr"/>
       <c r="G347" s="3" t="n">
-        <v>1.081828503224229</v>
+        <v>1.081828503224214</v>
       </c>
     </row>
     <row r="348">
@@ -9398,17 +9398,17 @@
         </is>
       </c>
       <c r="C348" s="3" t="n">
-        <v>0.05108805088474062</v>
+        <v>0.05108805088474176</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>0.07997513091750622</v>
+        <v>0.07997513091750617</v>
       </c>
       <c r="E348" s="3" t="n">
-        <v>0.5229535587402074</v>
+        <v>0.5229535587401979</v>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
       <c r="G348" s="3" t="n">
-        <v>0.6387992154390792</v>
+        <v>0.6387992154390939</v>
       </c>
     </row>
     <row r="349">
@@ -9423,13 +9423,13 @@
         </is>
       </c>
       <c r="C349" s="4" t="n">
-        <v>0.1236352619196694</v>
+        <v>0.1236352619196662</v>
       </c>
       <c r="D349" s="4" t="n">
-        <v>0.0711700951220671</v>
+        <v>0.07117009512206783</v>
       </c>
       <c r="E349" s="4" t="n">
-        <v>0.08235541370641634</v>
+        <v>0.08235541370642753</v>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="G349" s="4" t="n">
-        <v>1.737179944857695</v>
+        <v>1.737179944857632</v>
       </c>
     </row>
     <row r="350">
@@ -9452,13 +9452,13 @@
         </is>
       </c>
       <c r="C350" s="5" t="n">
-        <v>-0.2621165718490014</v>
+        <v>-0.2621165718490023</v>
       </c>
       <c r="D350" s="5" t="n">
-        <v>0.1201432991586916</v>
+        <v>0.1201432991586918</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>0.02913172022795547</v>
+        <v>0.02913172022795519</v>
       </c>
       <c r="F350" s="5" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         </is>
       </c>
       <c r="G350" s="5" t="n">
-        <v>-2.181699467922752</v>
+        <v>-2.181699467922755</v>
       </c>
     </row>
     <row r="351">
@@ -9481,13 +9481,13 @@
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>-0.263671645333821</v>
+        <v>-0.2636716453338133</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>0.0566596542003814</v>
+        <v>0.05665965420037925</v>
       </c>
       <c r="E351" s="2" t="n">
-        <v>3.261815151970401e-06</v>
+        <v>3.261815151969779e-06</v>
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
@@ -9495,32 +9495,36 @@
         </is>
       </c>
       <c r="G351" s="2" t="n">
-        <v>-4.653604916142361</v>
+        <v>-4.653604916142401</v>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="3" t="inlineStr">
+      <c r="A352" s="2" t="inlineStr">
         <is>
           <t>VULN-M.Int.GDP</t>
         </is>
       </c>
-      <c r="B352" s="3" t="inlineStr">
-        <is>
-          <t>3 Hazards Combined (Log)</t>
-        </is>
-      </c>
-      <c r="C352" s="3" t="n">
-        <v>0.01273697437762732</v>
-      </c>
-      <c r="D352" s="3" t="n">
-        <v>0.01994863073261054</v>
-      </c>
-      <c r="E352" s="3" t="n">
-        <v>0.523155637727823</v>
-      </c>
-      <c r="F352" s="3" t="inlineStr"/>
-      <c r="G352" s="3" t="n">
-        <v>0.6384886535999617</v>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Poverty Gap ($4.20/day)</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="n">
+        <v>-0.008072490353332816</v>
+      </c>
+      <c r="D352" s="2" t="n">
+        <v>0.003129565006732765</v>
+      </c>
+      <c r="E352" s="2" t="n">
+        <v>0.009896383489484397</v>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="n">
+        <v>-2.579428877804464</v>
       </c>
     </row>
     <row r="353">
@@ -9535,13 +9539,13 @@
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>0.0001663664527163533</v>
+        <v>0.0001663664527163258</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>6.11951742742923e-05</v>
+        <v>6.119517427429493e-05</v>
       </c>
       <c r="E353" s="2" t="n">
-        <v>0.006555478126818823</v>
+        <v>0.006555478126830048</v>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
@@ -9549,7 +9553,7 @@
         </is>
       </c>
       <c r="G353" s="2" t="n">
-        <v>2.718620458055347</v>
+        <v>2.718620458054781</v>
       </c>
     </row>
     <row r="354">
@@ -9564,13 +9568,13 @@
         </is>
       </c>
       <c r="C354" s="5" t="n">
-        <v>0.06100506220419347</v>
+        <v>0.0610050622041937</v>
       </c>
       <c r="D354" s="5" t="n">
-        <v>0.02830705060480577</v>
+        <v>0.02830705060480571</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>0.03115252433875869</v>
+        <v>0.03115252433875772</v>
       </c>
       <c r="F354" s="5" t="inlineStr">
         <is>
@@ -9578,36 +9582,32 @@
         </is>
       </c>
       <c r="G354" s="5" t="n">
-        <v>2.155118986286634</v>
+        <v>2.155118986286647</v>
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="inlineStr">
+      <c r="A355" s="3" t="inlineStr">
         <is>
           <t>VULN-M.Int.GDP</t>
         </is>
       </c>
-      <c r="B355" s="2" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C355" s="2" t="n">
-        <v>-0.008072490353332622</v>
-      </c>
-      <c r="D355" s="2" t="n">
-        <v>0.003129565006732793</v>
-      </c>
-      <c r="E355" s="2" t="n">
-        <v>0.009896383489486824</v>
-      </c>
-      <c r="F355" s="2" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="G355" s="2" t="n">
-        <v>-2.579428877804379</v>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="n">
+        <v>0.000215855243680336</v>
+      </c>
+      <c r="D355" s="3" t="n">
+        <v>0.001221716975812148</v>
+      </c>
+      <c r="E355" s="3" t="n">
+        <v>0.8597582800366056</v>
+      </c>
+      <c r="F355" s="3" t="inlineStr"/>
+      <c r="G355" s="3" t="n">
+        <v>0.1766818730965445</v>
       </c>
     </row>
     <row r="356">
@@ -9618,21 +9618,21 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Urban Population %</t>
+          <t>3 Hazards Combined (Log)</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
-        <v>0.0002158552436802826</v>
+        <v>0.01273697437762782</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>0.001221716975812141</v>
+        <v>0.01994863073261042</v>
       </c>
       <c r="E356" s="3" t="n">
-        <v>0.8597582800366392</v>
+        <v>0.5231556377278042</v>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
       <c r="G356" s="3" t="n">
-        <v>0.1766818730965017</v>
+        <v>0.6384886535999906</v>
       </c>
     </row>
     <row r="357">
@@ -9647,17 +9647,17 @@
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>-0.01165456022216877</v>
+        <v>-0.01165456022216832</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>0.0164766297577993</v>
+        <v>0.01647662975779924</v>
       </c>
       <c r="E357" s="3" t="n">
-        <v>0.4793559326777993</v>
+        <v>0.4793559326778145</v>
       </c>
       <c r="F357" s="3" t="inlineStr"/>
       <c r="G357" s="3" t="n">
-        <v>-0.7073388425598401</v>
+        <v>-0.7073388425598154</v>
       </c>
     </row>
     <row r="358">
@@ -9672,7 +9672,7 @@
         </is>
       </c>
       <c r="C358" s="3" t="n">
-        <v>0.6432251481683247</v>
+        <v>0.6432251481683245</v>
       </c>
       <c r="D358" s="3" t="inlineStr"/>
       <c r="E358" s="3" t="inlineStr"/>
@@ -9729,10 +9729,10 @@
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>0.564674654579736</v>
+        <v>0.5646746545797358</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>0.04155074809924641</v>
+        <v>0.04155074809924639</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>4.590822369532204e-42</v>
@@ -9758,17 +9758,17 @@
         </is>
       </c>
       <c r="C362" s="3" t="n">
-        <v>-0.07258320456268394</v>
+        <v>-0.07258320456268549</v>
       </c>
       <c r="D362" s="3" t="n">
-        <v>0.0545763781264982</v>
+        <v>0.05457637812649942</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>0.1835386673259138</v>
+        <v>0.1835386673259143</v>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
       <c r="G362" s="3" t="n">
-        <v>-1.329938098758572</v>
+        <v>-1.329938098758571</v>
       </c>
     </row>
     <row r="363">
@@ -9783,13 +9783,13 @@
         </is>
       </c>
       <c r="C363" s="4" t="n">
-        <v>0.1025310441901312</v>
+        <v>0.1025310441901286</v>
       </c>
       <c r="D363" s="4" t="n">
-        <v>0.05933297373183561</v>
+        <v>0.05933297373183605</v>
       </c>
       <c r="E363" s="4" t="n">
-        <v>0.08397714882362863</v>
+        <v>0.08397714882363876</v>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="G363" s="4" t="n">
-        <v>1.728061779838236</v>
+        <v>1.72806177983818</v>
       </c>
     </row>
     <row r="364">
@@ -9812,17 +9812,17 @@
         </is>
       </c>
       <c r="C364" s="3" t="n">
-        <v>0.09374319419972567</v>
+        <v>0.09374319419972441</v>
       </c>
       <c r="D364" s="3" t="n">
-        <v>0.08216059540937812</v>
+        <v>0.08216059540937834</v>
       </c>
       <c r="E364" s="3" t="n">
-        <v>0.2538802818224994</v>
+        <v>0.2538802818225073</v>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
       <c r="G364" s="3" t="n">
-        <v>1.140975107746425</v>
+        <v>1.140975107746407</v>
       </c>
     </row>
     <row r="365">
@@ -9837,13 +9837,13 @@
         </is>
       </c>
       <c r="C365" s="4" t="n">
-        <v>0.117049273262151</v>
+        <v>0.1170492732621465</v>
       </c>
       <c r="D365" s="4" t="n">
-        <v>0.06765792453990564</v>
+        <v>0.06765792453990652</v>
       </c>
       <c r="E365" s="4" t="n">
-        <v>0.08362746605212644</v>
+        <v>0.08362746605214241</v>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="G365" s="4" t="n">
-        <v>1.730015723333541</v>
+        <v>1.730015723333452</v>
       </c>
     </row>
     <row r="366">
@@ -9866,13 +9866,13 @@
         </is>
       </c>
       <c r="C366" s="5" t="n">
-        <v>-0.2502339231659311</v>
+        <v>-0.2502339231659306</v>
       </c>
       <c r="D366" s="5" t="n">
-        <v>0.1097392694498227</v>
+        <v>0.1097392694498224</v>
       </c>
       <c r="E366" s="5" t="n">
-        <v>0.0225923501127793</v>
+        <v>0.02259235011277912</v>
       </c>
       <c r="F366" s="5" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="G366" s="5" t="n">
-        <v>-2.280258693359976</v>
+        <v>-2.280258693359978</v>
       </c>
     </row>
     <row r="367">
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="C367" s="2" t="n">
-        <v>-0.243164133595253</v>
+        <v>-0.2431641335952508</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>0.05384297317697423</v>
+        <v>0.05384297317697376</v>
       </c>
       <c r="E367" s="2" t="n">
-        <v>6.296749441047479e-06</v>
+        <v>6.296749441047491e-06</v>
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
@@ -9909,115 +9909,119 @@
         </is>
       </c>
       <c r="G367" s="2" t="n">
-        <v>-4.516172106544096</v>
+        <v>-4.516172106544095</v>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="3" t="inlineStr">
+      <c r="A368" s="2" t="inlineStr">
         <is>
           <t>VULN-M.Int.WGI</t>
         </is>
       </c>
-      <c r="B368" s="3" t="inlineStr">
-        <is>
-          <t>3 Hazards Combined (Log)</t>
-        </is>
-      </c>
-      <c r="C368" s="3" t="n">
-        <v>0.0166720354264078</v>
-      </c>
-      <c r="D368" s="3" t="n">
-        <v>0.02189041785082076</v>
-      </c>
-      <c r="E368" s="3" t="n">
-        <v>0.4462907786679444</v>
-      </c>
-      <c r="F368" s="3" t="inlineStr"/>
-      <c r="G368" s="3" t="n">
-        <v>0.7616133935873087</v>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Poverty Gap ($4.20/day)</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="n">
+        <v>-0.008421412897507816</v>
+      </c>
+      <c r="D368" s="2" t="n">
+        <v>0.003036782238430463</v>
+      </c>
+      <c r="E368" s="2" t="n">
+        <v>0.005551875838014508</v>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="n">
+        <v>-2.773136904890605</v>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="inlineStr">
+      <c r="A369" s="4" t="inlineStr">
         <is>
           <t>VULN-M.Int.WGI</t>
         </is>
       </c>
-      <c r="B369" s="2" t="inlineStr">
+      <c r="B369" s="4" t="inlineStr">
+        <is>
+          <t>Government Effectiveness (WGI)</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="n">
+        <v>0.04884089185694211</v>
+      </c>
+      <c r="D369" s="4" t="n">
+        <v>0.02701415191424949</v>
+      </c>
+      <c r="E369" s="4" t="n">
+        <v>0.07061050368019159</v>
+      </c>
+      <c r="F369" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G369" s="4" t="n">
+        <v>1.807974279998751</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>VULN-M.Int.WGI</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
         <is>
           <t>Poverty Gap Squared</t>
         </is>
       </c>
-      <c r="C369" s="2" t="n">
-        <v>0.000166245236740454</v>
-      </c>
-      <c r="D369" s="2" t="n">
-        <v>5.785190439961654e-05</v>
-      </c>
-      <c r="E369" s="2" t="n">
-        <v>0.004057780726351429</v>
-      </c>
-      <c r="F369" s="2" t="inlineStr">
+      <c r="C370" s="2" t="n">
+        <v>0.000166245236740464</v>
+      </c>
+      <c r="D370" s="2" t="n">
+        <v>5.785190439961657e-05</v>
+      </c>
+      <c r="E370" s="2" t="n">
+        <v>0.004057780726349235</v>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="G369" s="2" t="n">
-        <v>2.873634644628154</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="3" t="inlineStr">
+      <c r="G370" s="2" t="n">
+        <v>2.873634644628325</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="3" t="inlineStr">
         <is>
           <t>VULN-M.Int.WGI</t>
         </is>
       </c>
-      <c r="B370" s="3" t="inlineStr">
+      <c r="B371" s="3" t="inlineStr">
         <is>
           <t>Log GDP per Capita (PPP)</t>
         </is>
       </c>
-      <c r="C370" s="3" t="n">
-        <v>0.02496289508630061</v>
-      </c>
-      <c r="D370" s="3" t="n">
-        <v>0.03463621932798652</v>
-      </c>
-      <c r="E370" s="3" t="n">
-        <v>0.4710839528431332</v>
-      </c>
-      <c r="F370" s="3" t="inlineStr"/>
-      <c r="G370" s="3" t="n">
-        <v>0.7207165092100646</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="2" t="inlineStr">
-        <is>
-          <t>VULN-M.Int.WGI</t>
-        </is>
-      </c>
-      <c r="B371" s="2" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C371" s="2" t="n">
-        <v>-0.008421412897507585</v>
-      </c>
-      <c r="D371" s="2" t="n">
-        <v>0.003036782238430462</v>
-      </c>
-      <c r="E371" s="2" t="n">
-        <v>0.005551875838015798</v>
-      </c>
-      <c r="F371" s="2" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="G371" s="2" t="n">
-        <v>-2.773136904890529</v>
+      <c r="C371" s="3" t="n">
+        <v>0.02496289508630076</v>
+      </c>
+      <c r="D371" s="3" t="n">
+        <v>0.03463621932798649</v>
+      </c>
+      <c r="E371" s="3" t="n">
+        <v>0.4710839528431302</v>
+      </c>
+      <c r="F371" s="3" t="inlineStr"/>
+      <c r="G371" s="3" t="n">
+        <v>0.7207165092100695</v>
       </c>
     </row>
     <row r="372">
@@ -10032,46 +10036,42 @@
         </is>
       </c>
       <c r="C372" s="3" t="n">
-        <v>0.0001435660181270849</v>
+        <v>0.0001435660181270382</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>0.001191564371144717</v>
+        <v>0.001191564371144721</v>
       </c>
       <c r="E372" s="3" t="n">
-        <v>0.9040987054992108</v>
+        <v>0.9040987054992421</v>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
       <c r="G372" s="3" t="n">
-        <v>0.1204853229953185</v>
+        <v>0.120485322995279</v>
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="inlineStr">
+      <c r="A373" s="3" t="inlineStr">
         <is>
           <t>VULN-M.Int.WGI</t>
         </is>
       </c>
-      <c r="B373" s="4" t="inlineStr">
-        <is>
-          <t>Government Effectiveness (WGI)</t>
-        </is>
-      </c>
-      <c r="C373" s="4" t="n">
-        <v>0.04884089185694163</v>
-      </c>
-      <c r="D373" s="4" t="n">
-        <v>0.02701415191424959</v>
-      </c>
-      <c r="E373" s="4" t="n">
-        <v>0.07061050368019535</v>
-      </c>
-      <c r="F373" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G373" s="4" t="n">
-        <v>1.807974279998727</v>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>3 Hazards Combined (Log)</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="n">
+        <v>0.01667203542640792</v>
+      </c>
+      <c r="D373" s="3" t="n">
+        <v>0.02189041785082071</v>
+      </c>
+      <c r="E373" s="3" t="n">
+        <v>0.44629077866794</v>
+      </c>
+      <c r="F373" s="3" t="inlineStr"/>
+      <c r="G373" s="3" t="n">
+        <v>0.7616133935873159</v>
       </c>
     </row>
     <row r="374">
@@ -10086,17 +10086,17 @@
         </is>
       </c>
       <c r="C374" s="3" t="n">
-        <v>-0.01113636425076855</v>
+        <v>-0.01113636425076882</v>
       </c>
       <c r="D374" s="3" t="n">
-        <v>0.02035939516188899</v>
+        <v>0.02035939516188897</v>
       </c>
       <c r="E374" s="3" t="n">
-        <v>0.5843863213737914</v>
+        <v>0.5843863213737819</v>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
       <c r="G374" s="3" t="n">
-        <v>-0.5469889533661024</v>
+        <v>-0.5469889533661162</v>
       </c>
     </row>
     <row r="375">
@@ -10168,13 +10168,13 @@
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>0.5740623447680294</v>
+        <v>0.5740623447680288</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>0.04917392393057215</v>
+        <v>0.04917392393057176</v>
       </c>
       <c r="E378" s="2" t="n">
-        <v>1.728427868735153e-31</v>
+        <v>1.728427868733569e-31</v>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="G378" s="2" t="n">
-        <v>11.67412113742516</v>
+        <v>11.67412113742524</v>
       </c>
     </row>
     <row r="379">
@@ -10197,17 +10197,17 @@
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>-0.08344126647886831</v>
+        <v>-0.0834412664788684</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>0.0547892608182769</v>
+        <v>0.05478926081827726</v>
       </c>
       <c r="E379" s="3" t="n">
-        <v>0.1277713899689759</v>
+        <v>0.1277713899689779</v>
       </c>
       <c r="F379" s="3" t="inlineStr"/>
       <c r="G379" s="3" t="n">
-        <v>-1.522949301243968</v>
+        <v>-1.522949301243959</v>
       </c>
     </row>
     <row r="380">
@@ -10222,17 +10222,17 @@
         </is>
       </c>
       <c r="C380" s="3" t="n">
-        <v>0.1086069585674827</v>
+        <v>0.1086069585674825</v>
       </c>
       <c r="D380" s="3" t="n">
-        <v>0.07050053009368283</v>
+        <v>0.07050053009368275</v>
       </c>
       <c r="E380" s="3" t="n">
-        <v>0.1234354412676946</v>
+        <v>0.1234354412676947</v>
       </c>
       <c r="F380" s="3" t="inlineStr"/>
       <c r="G380" s="3" t="n">
-        <v>1.540512651793726</v>
+        <v>1.540512651793725</v>
       </c>
     </row>
     <row r="381">
@@ -10247,17 +10247,17 @@
         </is>
       </c>
       <c r="C381" s="3" t="n">
-        <v>0.06414622901713521</v>
+        <v>0.06414622901713433</v>
       </c>
       <c r="D381" s="3" t="n">
-        <v>0.08627650757584954</v>
+        <v>0.08627650757584959</v>
       </c>
       <c r="E381" s="3" t="n">
-        <v>0.4571815072996113</v>
+        <v>0.4571815072996177</v>
       </c>
       <c r="F381" s="3" t="inlineStr"/>
       <c r="G381" s="3" t="n">
-        <v>0.7434958926767102</v>
+        <v>0.7434958926766997</v>
       </c>
     </row>
     <row r="382">
@@ -10272,17 +10272,17 @@
         </is>
       </c>
       <c r="C382" s="3" t="n">
-        <v>0.08969773840110541</v>
+        <v>0.08969773840110433</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>0.06158372536035846</v>
+        <v>0.06158372536035785</v>
       </c>
       <c r="E382" s="3" t="n">
-        <v>0.1452497738381231</v>
+        <v>0.145249773838124</v>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
       <c r="G382" s="3" t="n">
-        <v>1.456516926773059</v>
+        <v>1.456516926773056</v>
       </c>
     </row>
     <row r="383">
@@ -10297,13 +10297,13 @@
         </is>
       </c>
       <c r="C383" s="5" t="n">
-        <v>-0.2236140748392826</v>
+        <v>-0.2236140748392824</v>
       </c>
       <c r="D383" s="5" t="n">
-        <v>0.09898566684990817</v>
+        <v>0.09898566684990816</v>
       </c>
       <c r="E383" s="5" t="n">
-        <v>0.02387995806532446</v>
+        <v>0.02387995806532458</v>
       </c>
       <c r="F383" s="5" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="G383" s="5" t="n">
-        <v>-2.259055093080782</v>
+        <v>-2.25905509308078</v>
       </c>
     </row>
     <row r="384">
@@ -10326,13 +10326,13 @@
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>-0.2708638808510364</v>
+        <v>-0.2708638808510373</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>0.06014593396523643</v>
+        <v>0.06014593396523717</v>
       </c>
       <c r="E384" s="2" t="n">
-        <v>6.686080668278127e-06</v>
+        <v>6.686080668279345e-06</v>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
@@ -10340,32 +10340,36 @@
         </is>
       </c>
       <c r="G384" s="2" t="n">
-        <v>-4.503444588749626</v>
+        <v>-4.503444588749587</v>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="3" t="inlineStr">
+      <c r="A385" s="4" t="inlineStr">
         <is>
           <t>VULN-M.Int.BQCI</t>
         </is>
       </c>
-      <c r="B385" s="3" t="inlineStr">
-        <is>
-          <t>3 Hazards Combined (Log)</t>
-        </is>
-      </c>
-      <c r="C385" s="3" t="n">
-        <v>-0.009042136061363292</v>
-      </c>
-      <c r="D385" s="3" t="n">
-        <v>0.02370940575587548</v>
-      </c>
-      <c r="E385" s="3" t="n">
-        <v>0.7029262154986373</v>
-      </c>
-      <c r="F385" s="3" t="inlineStr"/>
-      <c r="G385" s="3" t="n">
-        <v>-0.3813733736925288</v>
+      <c r="B385" s="4" t="inlineStr">
+        <is>
+          <t>Poverty Gap ($4.20/day)</t>
+        </is>
+      </c>
+      <c r="C385" s="4" t="n">
+        <v>-0.005787145623490756</v>
+      </c>
+      <c r="D385" s="4" t="n">
+        <v>0.003391173602751625</v>
+      </c>
+      <c r="E385" s="4" t="n">
+        <v>0.08790910910346784</v>
+      </c>
+      <c r="F385" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G385" s="4" t="n">
+        <v>-1.706531809163359</v>
       </c>
     </row>
     <row r="386">
@@ -10380,13 +10384,13 @@
         </is>
       </c>
       <c r="C386" s="5" t="n">
-        <v>0.00015229947069408</v>
+        <v>0.0001522994706941152</v>
       </c>
       <c r="D386" s="5" t="n">
-        <v>6.082593203882894e-05</v>
+        <v>6.082593203882976e-05</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>0.01228474751606742</v>
+        <v>0.01228474751604846</v>
       </c>
       <c r="F386" s="5" t="inlineStr">
         <is>
@@ -10394,119 +10398,115 @@
         </is>
       </c>
       <c r="G386" s="5" t="n">
-        <v>2.503857575036546</v>
+        <v>2.503857575037092</v>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="4" t="inlineStr">
+      <c r="A387" s="5" t="inlineStr">
         <is>
           <t>VULN-M.Int.BQCI</t>
         </is>
       </c>
-      <c r="B387" s="4" t="inlineStr">
+      <c r="B387" s="5" t="inlineStr">
+        <is>
+          <t>Log GDP per Capita (PPP)</t>
+        </is>
+      </c>
+      <c r="C387" s="5" t="n">
+        <v>0.06350933115939296</v>
+      </c>
+      <c r="D387" s="5" t="n">
+        <v>0.02938650922549746</v>
+      </c>
+      <c r="E387" s="5" t="n">
+        <v>0.03068197599215572</v>
+      </c>
+      <c r="F387" s="5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="G387" s="5" t="n">
+        <v>2.161173029162938</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>VULN-M.Int.BQCI</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="n">
+        <v>0.0001387617686262638</v>
+      </c>
+      <c r="D388" s="3" t="n">
+        <v>0.001151539924233057</v>
+      </c>
+      <c r="E388" s="3" t="n">
+        <v>0.904086248863342</v>
+      </c>
+      <c r="F388" s="3" t="inlineStr"/>
+      <c r="G388" s="3" t="n">
+        <v>0.1205010488183302</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="inlineStr">
+        <is>
+          <t>VULN-M.Int.BQCI</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>3 Hazards Combined (Log)</t>
+        </is>
+      </c>
+      <c r="C389" s="3" t="n">
+        <v>-0.009042136061363315</v>
+      </c>
+      <c r="D389" s="3" t="n">
+        <v>0.02370940575587543</v>
+      </c>
+      <c r="E389" s="3" t="n">
+        <v>0.702926215498636</v>
+      </c>
+      <c r="F389" s="3" t="inlineStr"/>
+      <c r="G389" s="3" t="n">
+        <v>-0.3813733736925305</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="4" t="inlineStr">
+        <is>
+          <t>VULN-M.Int.BQCI</t>
+        </is>
+      </c>
+      <c r="B390" s="4" t="inlineStr">
         <is>
           <t>Building Quality Index</t>
         </is>
       </c>
-      <c r="C387" s="4" t="n">
-        <v>0.01029730809276926</v>
-      </c>
-      <c r="D387" s="4" t="n">
-        <v>0.005815637206069065</v>
-      </c>
-      <c r="E387" s="4" t="n">
-        <v>0.07662321158415382</v>
-      </c>
-      <c r="F387" s="4" t="inlineStr">
+      <c r="C390" s="4" t="n">
+        <v>0.01029730809276935</v>
+      </c>
+      <c r="D390" s="4" t="n">
+        <v>0.005815637206069058</v>
+      </c>
+      <c r="E390" s="4" t="n">
+        <v>0.07662321158415082</v>
+      </c>
+      <c r="F390" s="4" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="G387" s="4" t="n">
-        <v>1.770624220166834</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="5" t="inlineStr">
-        <is>
-          <t>VULN-M.Int.BQCI</t>
-        </is>
-      </c>
-      <c r="B388" s="5" t="inlineStr">
-        <is>
-          <t>Log GDP per Capita (PPP)</t>
-        </is>
-      </c>
-      <c r="C388" s="5" t="n">
-        <v>0.0635093311593935</v>
-      </c>
-      <c r="D388" s="5" t="n">
-        <v>0.02938650922549751</v>
-      </c>
-      <c r="E388" s="5" t="n">
-        <v>0.03068197599215462</v>
-      </c>
-      <c r="F388" s="5" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G388" s="5" t="n">
-        <v>2.161173029162952</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="4" t="inlineStr">
-        <is>
-          <t>VULN-M.Int.BQCI</t>
-        </is>
-      </c>
-      <c r="B389" s="4" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C389" s="4" t="n">
-        <v>-0.005787145623490648</v>
-      </c>
-      <c r="D389" s="4" t="n">
-        <v>0.0033911736027516</v>
-      </c>
-      <c r="E389" s="4" t="n">
-        <v>0.08790910910347149</v>
-      </c>
-      <c r="F389" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G389" s="4" t="n">
-        <v>-1.706531809163339</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="3" t="inlineStr">
-        <is>
-          <t>VULN-M.Int.BQCI</t>
-        </is>
-      </c>
-      <c r="B390" s="3" t="inlineStr">
-        <is>
-          <t>Urban Population %</t>
-        </is>
-      </c>
-      <c r="C390" s="3" t="n">
-        <v>0.000138761768626215</v>
-      </c>
-      <c r="D390" s="3" t="n">
-        <v>0.00115153992423306</v>
-      </c>
-      <c r="E390" s="3" t="n">
-        <v>0.9040862488633759</v>
-      </c>
-      <c r="F390" s="3" t="inlineStr"/>
-      <c r="G390" s="3" t="n">
-        <v>0.1205010488182875</v>
+      <c r="G390" s="4" t="n">
+        <v>1.770624220166852</v>
       </c>
     </row>
     <row r="391">
@@ -10521,17 +10521,17 @@
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>0.008016253078963111</v>
+        <v>0.008016253078963269</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>0.006363708548296228</v>
+        <v>0.006363708548296201</v>
       </c>
       <c r="E391" s="3" t="n">
-        <v>0.207783876292395</v>
+        <v>0.2077838762923842</v>
       </c>
       <c r="F391" s="3" t="inlineStr"/>
       <c r="G391" s="3" t="n">
-        <v>1.259682623445934</v>
+        <v>1.259682623445965</v>
       </c>
     </row>
     <row r="392">
@@ -14932,13 +14932,13 @@
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>0.2568338699263277</v>
+        <v>0.2568338699263261</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>0.05335072431922872</v>
+        <v>0.05335072431922928</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>1.478904573596089e-06</v>
+        <v>1.478904573596688e-06</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>4.81406528596575</v>
+        <v>4.814065285965669</v>
       </c>
     </row>
     <row r="173">
@@ -14961,17 +14961,17 @@
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>0.1116781148964695</v>
+        <v>0.1116781148964683</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>0.07066627619774414</v>
+        <v>0.07066627619774317</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>0.1140245804086747</v>
+        <v>0.1140245804086737</v>
       </c>
       <c r="F173" s="3" t="inlineStr"/>
       <c r="G173" s="3" t="n">
-        <v>1.580359414778879</v>
+        <v>1.580359414778883</v>
       </c>
     </row>
     <row r="174">
@@ -14986,13 +14986,13 @@
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>-0.1886648649900303</v>
+        <v>-0.1886648649900315</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>0.05987606097753453</v>
+        <v>0.0598760609775335</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.001627553236726506</v>
+        <v>0.0016275532367261</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>-3.150923122027304</v>
+        <v>-3.150923122027377</v>
       </c>
     </row>
     <row r="175">
@@ -15015,13 +15015,13 @@
         </is>
       </c>
       <c r="C175" s="5" t="n">
-        <v>0.1986567810211367</v>
+        <v>0.198656781021138</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>0.09274673601371444</v>
+        <v>0.09274673601371318</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>0.03219931947977279</v>
+        <v>0.0321993194797693</v>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>2.141927463536414</v>
+        <v>2.141927463536457</v>
       </c>
     </row>
     <row r="176">
@@ -15044,13 +15044,13 @@
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>-0.3327696369918222</v>
+        <v>-0.3327696369918283</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>0.08679911984678758</v>
+        <v>0.08679911984678478</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.0001261836457430032</v>
+        <v>0.0001261836457429035</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>-3.833790452935542</v>
+        <v>-3.833790452935737</v>
       </c>
     </row>
     <row r="177">
@@ -15073,17 +15073,17 @@
         </is>
       </c>
       <c r="C177" s="3" t="n">
-        <v>0.1128888315754472</v>
+        <v>0.1128888315754474</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>0.1093807650986641</v>
+        <v>0.109380765098664</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>0.302038361422702</v>
+        <v>0.3020383614227007</v>
       </c>
       <c r="F177" s="3" t="inlineStr"/>
       <c r="G177" s="3" t="n">
-        <v>1.032072060143469</v>
+        <v>1.032072060143472</v>
       </c>
     </row>
     <row r="178">
@@ -15098,17 +15098,17 @@
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>-0.04085486610571988</v>
+        <v>-0.0408548661057211</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>0.06183233695295793</v>
+        <v>0.06183233695295797</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>0.5087814757492728</v>
+        <v>0.5087814757492605</v>
       </c>
       <c r="F178" s="3" t="inlineStr"/>
       <c r="G178" s="3" t="n">
-        <v>-0.6607362444800086</v>
+        <v>-0.6607362444800279</v>
       </c>
     </row>
     <row r="179">
@@ -15119,21 +15119,21 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Poverty Gap Squared</t>
+          <t>Poverty Gap ($4.20/day)</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>2.149092737414783e-05</v>
+        <v>-0.002209868203710813</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>6.659113763721338e-05</v>
+        <v>0.003488369887096856</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>0.7469000767701512</v>
+        <v>0.5264098232598966</v>
       </c>
       <c r="F179" s="3" t="inlineStr"/>
       <c r="G179" s="3" t="n">
-        <v>0.3227295423488601</v>
+        <v>-0.6334959523314607</v>
       </c>
     </row>
     <row r="180">
@@ -15144,50 +15144,46 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Storm Count (Log)</t>
+          <t>Poverty Gap Squared</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>-0.0007159972659363308</v>
+        <v>2.14909273741826e-05</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>0.01466657436325475</v>
+        <v>6.659113763721075e-05</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0.9610640961680925</v>
+        <v>0.7469000767697461</v>
       </c>
       <c r="F180" s="3" t="inlineStr"/>
       <c r="G180" s="3" t="n">
-        <v>-0.04881830263856104</v>
+        <v>0.322729542349395</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="4" t="inlineStr">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.Pov</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>Log GDP per Capita (PPP)</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="n">
-        <v>0.06213837413618363</v>
-      </c>
-      <c r="D181" s="4" t="n">
-        <v>0.03308900807012055</v>
-      </c>
-      <c r="E181" s="4" t="n">
-        <v>0.06039267186499894</v>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G181" s="4" t="n">
-        <v>1.87791589293046</v>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Flood Count (Log)</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>-0.005859826846947663</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>0.01520640263125835</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>0.6999761929011845</v>
+      </c>
+      <c r="F181" s="3" t="inlineStr"/>
+      <c r="G181" s="3" t="n">
+        <v>-0.3853526037053746</v>
       </c>
     </row>
     <row r="182">
@@ -15198,21 +15194,21 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Flood Count (Log)</t>
+          <t>Storm Count (Log)</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>-0.005859826846948003</v>
+        <v>-0.0007159972659363401</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>0.01520640263125827</v>
+        <v>0.01466657436325471</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0.6999761929011663</v>
+        <v>0.9610640961680919</v>
       </c>
       <c r="F182" s="3" t="inlineStr"/>
       <c r="G182" s="3" t="n">
-        <v>-0.3853526037053989</v>
+        <v>-0.0488183026385618</v>
       </c>
     </row>
     <row r="183">
@@ -15223,17 +15219,17 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Earthquake Count (Log)</t>
+          <t>Log GDP per Capita (PPP)</t>
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>0.03154783322425408</v>
+        <v>0.06213837413618427</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>0.01785646645643429</v>
+        <v>0.03308900807012059</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>0.07727084588900374</v>
+        <v>0.06039267186499653</v>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
@@ -15241,32 +15237,36 @@
         </is>
       </c>
       <c r="G183" s="4" t="n">
-        <v>1.766745582124191</v>
+        <v>1.877915892930477</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="inlineStr">
+      <c r="A184" s="4" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.Pov</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="n">
-        <v>-0.002209868203710643</v>
-      </c>
-      <c r="D184" s="3" t="n">
-        <v>0.00348836988709688</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>0.5264098232599312</v>
-      </c>
-      <c r="F184" s="3" t="inlineStr"/>
-      <c r="G184" s="3" t="n">
-        <v>-0.6334959523314077</v>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>0.001893105623321324</v>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>0.001017391609338345</v>
+      </c>
+      <c r="E184" s="4" t="n">
+        <v>0.06278029670998979</v>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="n">
+        <v>1.860744285627139</v>
       </c>
     </row>
     <row r="185">
@@ -15277,17 +15277,17 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Urban Population %</t>
+          <t>Earthquake Count (Log)</t>
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>0.001893105623321288</v>
+        <v>0.03154783322425367</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>0.001017391609338349</v>
+        <v>0.01785646645643425</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>0.0627802967099957</v>
+        <v>0.07727084588900701</v>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="G185" s="4" t="n">
-        <v>1.860744285627097</v>
+        <v>1.766745582124171</v>
       </c>
     </row>
     <row r="186">
@@ -15310,13 +15310,13 @@
         </is>
       </c>
       <c r="C186" s="5" t="n">
-        <v>-0.002780824305382441</v>
+        <v>-0.002780824305382559</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>0.001294094557574173</v>
+        <v>0.001294094557574202</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.0316457277390499</v>
+        <v>0.03164572773904654</v>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>-2.148857121070964</v>
+        <v>-2.148857121071007</v>
       </c>
     </row>
     <row r="187">
@@ -15339,17 +15339,17 @@
         </is>
       </c>
       <c r="C187" s="3" t="n">
-        <v>0.0008372208535764726</v>
+        <v>0.0008372208535764359</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>0.0006979223647288362</v>
+        <v>0.0006979223647288446</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>0.230298520836125</v>
+        <v>0.230298520836151</v>
       </c>
       <c r="F187" s="3" t="inlineStr"/>
       <c r="G187" s="3" t="n">
-        <v>1.199590235085471</v>
+        <v>1.199590235085404</v>
       </c>
     </row>
     <row r="188">
@@ -15364,13 +15364,13 @@
         </is>
       </c>
       <c r="C188" s="5" t="n">
-        <v>0.002782286522300731</v>
+        <v>0.002782286522300811</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>0.001203511211745708</v>
+        <v>0.001203511211745726</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>0.02078828125918792</v>
+        <v>0.02078828125918619</v>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2.311807729871489</v>
+        <v>2.311807729871521</v>
       </c>
     </row>
     <row r="189">
@@ -15450,13 +15450,13 @@
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>0.2645989994193266</v>
+        <v>0.2645989994193222</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>0.05097941922312407</v>
+        <v>0.05097941922312606</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>2.09944032293719e-07</v>
+        <v>2.099440322940453e-07</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>5.190310196772614</v>
+        <v>5.190310196772324</v>
       </c>
     </row>
     <row r="193">
@@ -15479,13 +15479,13 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>0.1123721634356968</v>
+        <v>0.1123721634357016</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>0.06681604599206521</v>
+        <v>0.06681604599206797</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>0.09260490769313195</v>
+        <v>0.09260490769313139</v>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         </is>
       </c>
       <c r="G193" s="4" t="n">
-        <v>1.681814027861535</v>
+        <v>1.681814027861538</v>
       </c>
     </row>
     <row r="194">
@@ -15508,13 +15508,13 @@
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>-0.1960173486622176</v>
+        <v>-0.1960173486622172</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>0.0577024648742006</v>
+        <v>0.05770246487420203</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.0006812001239899002</v>
+        <v>0.0006812001239901322</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>-3.397035968733098</v>
+        <v>-3.397035968733006</v>
       </c>
     </row>
     <row r="195">
@@ -15537,13 +15537,13 @@
         </is>
       </c>
       <c r="C195" s="5" t="n">
-        <v>0.1945714709941687</v>
+        <v>0.1945714709941779</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>0.08986776066434261</v>
+        <v>0.08986776066434586</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>0.03038106537314033</v>
+        <v>0.03038106537313852</v>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2.165086450978744</v>
+        <v>2.165086450978768</v>
       </c>
     </row>
     <row r="196">
@@ -15566,13 +15566,13 @@
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>-0.2817761622479868</v>
+        <v>-0.2817761622479825</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>0.0908808683896503</v>
+        <v>0.0908808683896518</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.001931939998499683</v>
+        <v>0.001931939998500334</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>-3.100500327966453</v>
+        <v>-3.100500327966354</v>
       </c>
     </row>
     <row r="197">
@@ -15595,17 +15595,17 @@
         </is>
       </c>
       <c r="C197" s="3" t="n">
-        <v>0.1003086135125206</v>
+        <v>0.1003086135125198</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>0.1235177898576919</v>
+        <v>0.1235177898576917</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>0.4167351061856883</v>
+        <v>0.4167351061856912</v>
       </c>
       <c r="F197" s="3" t="inlineStr"/>
       <c r="G197" s="3" t="n">
-        <v>0.8120985133241843</v>
+        <v>0.8120985133241793</v>
       </c>
     </row>
     <row r="198">
@@ -15620,17 +15620,17 @@
         </is>
       </c>
       <c r="C198" s="3" t="n">
-        <v>-0.05515435909616632</v>
+        <v>-0.05515435909616172</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>0.06362915849666854</v>
+        <v>0.06362915849666956</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>0.3860463957500188</v>
+        <v>0.3860463957500659</v>
       </c>
       <c r="F198" s="3" t="inlineStr"/>
       <c r="G198" s="3" t="n">
-        <v>-0.8668095005382486</v>
+        <v>-0.8668095005381625</v>
       </c>
     </row>
     <row r="199">
@@ -15641,21 +15641,21 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Poverty Gap Squared</t>
+          <t>Poverty Gap ($4.20/day)</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
-        <v>5.214123100223234e-05</v>
+        <v>-0.00221570751108946</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>6.327995585659682e-05</v>
+        <v>0.003358343073195923</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>0.4099526014368813</v>
+        <v>0.5094065020953089</v>
       </c>
       <c r="F199" s="3" t="inlineStr"/>
       <c r="G199" s="3" t="n">
-        <v>0.8239770444908853</v>
+        <v>-0.6597621097063534</v>
       </c>
     </row>
     <row r="200">
@@ -15666,50 +15666,46 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Storm Count (Log)</t>
+          <t>Poverty Gap Squared</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
-        <v>-0.0008205747071156823</v>
+        <v>5.214123100223337e-05</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>0.01458213456585213</v>
+        <v>6.327995585659598e-05</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>0.9551246418149282</v>
+        <v>0.4099526014368657</v>
       </c>
       <c r="F200" s="3" t="inlineStr"/>
       <c r="G200" s="3" t="n">
-        <v>-0.0562726055921382</v>
+        <v>0.8239770444909125</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="inlineStr">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.GDP</t>
         </is>
       </c>
-      <c r="B201" s="5" t="inlineStr">
-        <is>
-          <t>Log GDP per Capita (PPP)</t>
-        </is>
-      </c>
-      <c r="C201" s="5" t="n">
-        <v>0.06393107608576949</v>
-      </c>
-      <c r="D201" s="5" t="n">
-        <v>0.03030873898428963</v>
-      </c>
-      <c r="E201" s="5" t="n">
-        <v>0.03491626729457348</v>
-      </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="n">
-        <v>2.109328141923286</v>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Flood Count (Log)</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>-0.005799392309378355</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0.0157862220347569</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>0.7133426718504514</v>
+      </c>
+      <c r="F201" s="3" t="inlineStr"/>
+      <c r="G201" s="3" t="n">
+        <v>-0.3673705017330743</v>
       </c>
     </row>
     <row r="202">
@@ -15720,75 +15716,79 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Flood Count (Log)</t>
+          <t>Storm Count (Log)</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
-        <v>-0.005799392309378367</v>
+        <v>-0.0008205747071154831</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>0.01578622203475681</v>
+        <v>0.01458213456585208</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>0.7133426718504494</v>
+        <v>0.9551246418149388</v>
       </c>
       <c r="F202" s="3" t="inlineStr"/>
       <c r="G202" s="3" t="n">
-        <v>-0.3673705017330771</v>
+        <v>-0.05627260559212471</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="4" t="inlineStr">
+      <c r="A203" s="5" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.GDP</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>Earthquake Count (Log)</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="n">
-        <v>0.02923878934468092</v>
-      </c>
-      <c r="D203" s="4" t="n">
-        <v>0.01697289335543069</v>
-      </c>
-      <c r="E203" s="4" t="n">
-        <v>0.08494720408859505</v>
-      </c>
-      <c r="F203" s="4" t="inlineStr">
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>Log GDP per Capita (PPP)</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="n">
+        <v>0.06393107608576989</v>
+      </c>
+      <c r="D203" s="5" t="n">
+        <v>0.03030873898428947</v>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>0.03491626729457142</v>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>2.10932814192331</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>ONLY-J+K+N.Int.GDP</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="n">
+        <v>0.001598196514941687</v>
+      </c>
+      <c r="D204" s="4" t="n">
+        <v>0.0009414799059284987</v>
+      </c>
+      <c r="E204" s="4" t="n">
+        <v>0.08959527438386762</v>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
-        <v>1.72267560588458</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>ONLY-J+K+N.Int.GDP</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="n">
-        <v>-0.002215707511089451</v>
-      </c>
-      <c r="D204" s="3" t="n">
-        <v>0.0033583430731959</v>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>0.5094065020953078</v>
-      </c>
-      <c r="F204" s="3" t="inlineStr"/>
-      <c r="G204" s="3" t="n">
-        <v>-0.6597621097063551</v>
+      <c r="G204" s="4" t="n">
+        <v>1.697536511271079</v>
       </c>
     </row>
     <row r="205">
@@ -15799,17 +15799,17 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Urban Population %</t>
+          <t>Earthquake Count (Log)</t>
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>0.001598196514941712</v>
+        <v>0.02923878934468096</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>0.0009414799059285028</v>
+        <v>0.01697289335543066</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>0.08959527438386408</v>
+        <v>0.08494720408859407</v>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="G205" s="4" t="n">
-        <v>1.697536511271098</v>
+        <v>1.722675605884585</v>
       </c>
     </row>
     <row r="206">
@@ -15832,13 +15832,13 @@
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>0.04480261146307513</v>
+        <v>0.04480261146307515</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>0.01669571309749121</v>
+        <v>0.01669571309749114</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>0.007286034240375665</v>
+        <v>0.007286034240375397</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>2.6834799568883</v>
+        <v>2.683479956888312</v>
       </c>
     </row>
     <row r="207">
@@ -15861,17 +15861,17 @@
         </is>
       </c>
       <c r="C207" s="3" t="n">
-        <v>-0.0173493932216465</v>
+        <v>-0.01734939322164653</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>0.01095460900720479</v>
+        <v>0.0109546090072048</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>0.1132499730920765</v>
+        <v>0.1132499730920761</v>
       </c>
       <c r="F207" s="3" t="inlineStr"/>
       <c r="G207" s="3" t="n">
-        <v>-1.583752848708328</v>
+        <v>-1.58375284870833</v>
       </c>
     </row>
     <row r="208">
@@ -15886,17 +15886,17 @@
         </is>
       </c>
       <c r="C208" s="3" t="n">
-        <v>-0.02343994528590478</v>
+        <v>-0.02343994528590483</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>0.01559250138877653</v>
+        <v>0.01559250138877657</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>0.1327660320866918</v>
+        <v>0.1327660320866919</v>
       </c>
       <c r="F208" s="3" t="inlineStr"/>
       <c r="G208" s="3" t="n">
-        <v>-1.503283193726495</v>
+        <v>-1.503283193726494</v>
       </c>
     </row>
     <row r="209">
@@ -15968,13 +15968,13 @@
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>0.2477073018232431</v>
+        <v>0.247707301823241</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>0.04994866588931986</v>
+        <v>0.04994866588932052</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>7.077036875110625e-07</v>
+        <v>7.077036875114497e-07</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>4.959237597499244</v>
+        <v>4.959237597499138</v>
       </c>
     </row>
     <row r="213">
@@ -15997,13 +15997,13 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>0.1299444757095713</v>
+        <v>0.1299444757095689</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>0.06803330428561323</v>
+        <v>0.06803330428561136</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>0.05613157719840479</v>
+        <v>0.0561315771984027</v>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         </is>
       </c>
       <c r="G213" s="4" t="n">
-        <v>1.910012707365299</v>
+        <v>1.910012707365316</v>
       </c>
     </row>
     <row r="214">
@@ -16026,13 +16026,13 @@
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>-0.1808439840700763</v>
+        <v>-0.1808439840700833</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>0.06012922048091829</v>
+        <v>0.06012922048091467</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>0.002633289769605402</v>
+        <v>0.002633289769602823</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>-3.007589032814192</v>
+        <v>-3.007589032814489</v>
       </c>
     </row>
     <row r="215">
@@ -16055,13 +16055,13 @@
         </is>
       </c>
       <c r="C215" s="5" t="n">
-        <v>0.2269302532809947</v>
+        <v>0.2269302532809865</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>0.09475854981512559</v>
+        <v>0.0947585498151218</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>0.01662824727703666</v>
+        <v>0.01662824727703626</v>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>2.394826152613529</v>
+        <v>2.394826152613538</v>
       </c>
     </row>
     <row r="216">
@@ -16084,13 +16084,13 @@
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>-0.2601644375484162</v>
+        <v>-0.2601644375484238</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>0.09010363706612638</v>
+        <v>0.09010363706612372</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>0.003884510787026696</v>
+        <v>0.003884510787024588</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>-2.887391075650847</v>
+        <v>-2.887391075651017</v>
       </c>
     </row>
     <row r="217">
@@ -16113,17 +16113,17 @@
         </is>
       </c>
       <c r="C217" s="3" t="n">
-        <v>0.1095400435741864</v>
+        <v>0.1095400435741862</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>0.1099992554355174</v>
+        <v>0.1099992554355167</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>0.3193350263430533</v>
+        <v>0.3193350263430509</v>
       </c>
       <c r="F217" s="3" t="inlineStr"/>
       <c r="G217" s="3" t="n">
-        <v>0.9958253184577216</v>
+        <v>0.9958253184577266</v>
       </c>
     </row>
     <row r="218">
@@ -16138,17 +16138,17 @@
         </is>
       </c>
       <c r="C218" s="3" t="n">
-        <v>-0.01867932427166744</v>
+        <v>-0.01867932427166387</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>0.05982116419136539</v>
+        <v>0.05982116419136665</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>0.7548484301890699</v>
+        <v>0.7548484301891203</v>
       </c>
       <c r="F218" s="3" t="inlineStr"/>
       <c r="G218" s="3" t="n">
-        <v>-0.3122527708072191</v>
+        <v>-0.3122527708071527</v>
       </c>
     </row>
     <row r="219">
@@ -16159,21 +16159,21 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>Poverty Gap Squared</t>
+          <t>Poverty Gap ($4.20/day)</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
-        <v>7.290643335274136e-05</v>
+        <v>-0.002712341742199033</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>6.144977809906875e-05</v>
+        <v>0.003343572027120447</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>0.2354488488260726</v>
+        <v>0.4172446239750873</v>
       </c>
       <c r="F219" s="3" t="inlineStr"/>
       <c r="G219" s="3" t="n">
-        <v>1.186439326684017</v>
+        <v>-0.8112108009633511</v>
       </c>
     </row>
     <row r="220">
@@ -16184,50 +16184,46 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Storm Count (Log)</t>
+          <t>Government Effectiveness (WGI)</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
-        <v>-0.002629938586939431</v>
+        <v>0.01709585471758367</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>0.0135690975548827</v>
+        <v>0.02195455609390849</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>0.846318205501929</v>
+        <v>0.4361606994893859</v>
       </c>
       <c r="F220" s="3" t="inlineStr"/>
       <c r="G220" s="3" t="n">
-        <v>-0.1938182385602405</v>
+        <v>0.7786927981808334</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="4" t="inlineStr">
+      <c r="A221" s="3" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.WGI</t>
         </is>
       </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>Log GDP per Capita (PPP)</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="n">
-        <v>0.05429124562663749</v>
-      </c>
-      <c r="D221" s="4" t="n">
-        <v>0.03113197383368885</v>
-      </c>
-      <c r="E221" s="4" t="n">
-        <v>0.08117542808074299</v>
-      </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G221" s="4" t="n">
-        <v>1.743906310491861</v>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>Poverty Gap Squared</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>7.290643335277345e-05</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>6.144977809906559e-05</v>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>0.2354488488258423</v>
+      </c>
+      <c r="F221" s="3" t="inlineStr"/>
+      <c r="G221" s="3" t="n">
+        <v>1.1864393266846</v>
       </c>
     </row>
     <row r="222">
@@ -16242,71 +16238,71 @@
         </is>
       </c>
       <c r="C222" s="3" t="n">
-        <v>-0.006118195020519427</v>
+        <v>-0.006118195020519218</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>0.01555547516228488</v>
+        <v>0.01555547516228491</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>0.6940871585100667</v>
+        <v>0.6940871585100772</v>
       </c>
       <c r="F222" s="3" t="inlineStr"/>
       <c r="G222" s="3" t="n">
-        <v>-0.3933145697376916</v>
+        <v>-0.3933145697376775</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="4" t="inlineStr">
+      <c r="A223" s="3" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.WGI</t>
         </is>
       </c>
-      <c r="B223" s="4" t="inlineStr">
-        <is>
-          <t>Earthquake Count (Log)</t>
-        </is>
-      </c>
-      <c r="C223" s="4" t="n">
-        <v>0.03460604745294167</v>
-      </c>
-      <c r="D223" s="4" t="n">
-        <v>0.01819426195306144</v>
-      </c>
-      <c r="E223" s="4" t="n">
-        <v>0.05716712211939082</v>
-      </c>
-      <c r="F223" s="4" t="inlineStr">
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Storm Count (Log)</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>-0.002629938586939547</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>0.01356909755488271</v>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>0.8463182055019225</v>
+      </c>
+      <c r="F223" s="3" t="inlineStr"/>
+      <c r="G223" s="3" t="n">
+        <v>-0.1938182385602488</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>ONLY-J+K+N.Int.WGI</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Log GDP per Capita (PPP)</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="n">
+        <v>0.05429124562663742</v>
+      </c>
+      <c r="D224" s="4" t="n">
+        <v>0.03113197383368902</v>
+      </c>
+      <c r="E224" s="4" t="n">
+        <v>0.08117542808074507</v>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
-        <v>1.902030845890878</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="3" t="inlineStr">
-        <is>
-          <t>ONLY-J+K+N.Int.WGI</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="n">
-        <v>-0.002712341742198371</v>
-      </c>
-      <c r="D224" s="3" t="n">
-        <v>0.003343572027120561</v>
-      </c>
-      <c r="E224" s="3" t="n">
-        <v>0.4172446239752171</v>
-      </c>
-      <c r="F224" s="3" t="inlineStr"/>
-      <c r="G224" s="3" t="n">
-        <v>-0.8112108009631251</v>
+      <c r="G224" s="4" t="n">
+        <v>1.74390631049185</v>
       </c>
     </row>
     <row r="225">
@@ -16321,13 +16317,13 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>0.001740569652374734</v>
+        <v>0.001740569652374696</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>0.0009739046335525095</v>
+        <v>0.0009739046335525185</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>0.0739039597358917</v>
+        <v>0.07390395973590064</v>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
@@ -16335,32 +16331,36 @@
         </is>
       </c>
       <c r="G225" s="4" t="n">
-        <v>1.78720748665674</v>
+        <v>1.787207486656684</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="inlineStr">
+      <c r="A226" s="4" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.WGI</t>
         </is>
       </c>
-      <c r="B226" s="3" t="inlineStr">
-        <is>
-          <t>Government Effectiveness (WGI)</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="n">
-        <v>0.0170958547175847</v>
-      </c>
-      <c r="D226" s="3" t="n">
-        <v>0.02195455609390847</v>
-      </c>
-      <c r="E226" s="3" t="n">
-        <v>0.4361606994893579</v>
-      </c>
-      <c r="F226" s="3" t="inlineStr"/>
-      <c r="G226" s="3" t="n">
-        <v>0.778692798180881</v>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Earthquake Count (Log)</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>0.03460604745294173</v>
+      </c>
+      <c r="D226" s="4" t="n">
+        <v>0.01819426195306153</v>
+      </c>
+      <c r="E226" s="4" t="n">
+        <v>0.05716712211939159</v>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="n">
+        <v>1.902030845890872</v>
       </c>
     </row>
     <row r="227">
@@ -16375,13 +16375,13 @@
         </is>
       </c>
       <c r="C227" s="5" t="n">
-        <v>0.04473556832540326</v>
+        <v>0.04473556832540329</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>0.01846485037272445</v>
+        <v>0.01846485037272462</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>0.01540386265256264</v>
+        <v>0.01540386265256352</v>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>2.422741989368345</v>
+        <v>2.422741989368324</v>
       </c>
     </row>
     <row r="228">
@@ -16404,13 +16404,13 @@
         </is>
       </c>
       <c r="C228" s="5" t="n">
-        <v>-0.03141351199603911</v>
+        <v>-0.03141351199603921</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>0.01346417527297773</v>
+        <v>0.0134641752729778</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>0.0196419439803193</v>
+        <v>0.01964194398031956</v>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>-2.33311817167779</v>
+        <v>-2.333118171677785</v>
       </c>
     </row>
     <row r="229">
@@ -16433,17 +16433,17 @@
         </is>
       </c>
       <c r="C229" s="3" t="n">
-        <v>-0.01186305657155387</v>
+        <v>-0.01186305657155374</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>0.01496491377065546</v>
+        <v>0.01496491377065547</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>0.4279382443494322</v>
+        <v>0.4279382443494373</v>
       </c>
       <c r="F229" s="3" t="inlineStr"/>
       <c r="G229" s="3" t="n">
-        <v>-0.792724686113194</v>
+        <v>-0.7927246861131853</v>
       </c>
     </row>
     <row r="230">
@@ -16515,13 +16515,13 @@
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>0.2712175400192203</v>
+        <v>0.2712175400192254</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>0.05615921263895385</v>
+        <v>0.05615921263895065</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>1.369176582810902e-06</v>
+        <v>1.36917658280838e-06</v>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>4.82943985990101</v>
+        <v>4.829439859901377</v>
       </c>
     </row>
     <row r="234">
@@ -16544,17 +16544,17 @@
         </is>
       </c>
       <c r="C234" s="3" t="n">
-        <v>0.09276129615254004</v>
+        <v>0.09276129615254174</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>0.07269714176053635</v>
+        <v>0.07269714176053826</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>0.2019567674928135</v>
+        <v>0.2019567674928172</v>
       </c>
       <c r="F234" s="3" t="inlineStr"/>
       <c r="G234" s="3" t="n">
-        <v>1.27599646844569</v>
+        <v>1.275996468445679</v>
       </c>
     </row>
     <row r="235">
@@ -16569,13 +16569,13 @@
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>-0.1801230145023573</v>
+        <v>-0.1801230145023567</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>0.06121089917893594</v>
+        <v>0.06121089917893636</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>0.003254030098795901</v>
+        <v>0.00325403009879622</v>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>-2.942662449310035</v>
+        <v>-2.942662449310005</v>
       </c>
     </row>
     <row r="236">
@@ -16598,13 +16598,13 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>0.1569671086541272</v>
+        <v>0.1569671086541255</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>0.09458549539778664</v>
+        <v>0.09458549539778635</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>0.09700980374674391</v>
+        <v>0.09700980374674646</v>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="G236" s="4" t="n">
-        <v>1.65952620953128</v>
+        <v>1.659526209531268</v>
       </c>
     </row>
     <row r="237">
@@ -16627,13 +16627,13 @@
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>-0.3294242440381057</v>
+        <v>-0.3294242440381009</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>0.08834125397568915</v>
+        <v>0.08834125397568954</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>0.0001922436737684538</v>
+        <v>0.000192243673768508</v>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>-3.72899669421447</v>
+        <v>-3.728996694214399</v>
       </c>
     </row>
     <row r="238">
@@ -16656,17 +16656,17 @@
         </is>
       </c>
       <c r="C238" s="3" t="n">
-        <v>0.1112452614542823</v>
+        <v>0.1112452614542772</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>0.1067692551343454</v>
+        <v>0.106769255134345</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>0.2974477321803102</v>
+        <v>0.2974477321803304</v>
       </c>
       <c r="F238" s="3" t="inlineStr"/>
       <c r="G238" s="3" t="n">
-        <v>1.041922239827419</v>
+        <v>1.041922239827375</v>
       </c>
     </row>
     <row r="239">
@@ -16681,17 +16681,17 @@
         </is>
       </c>
       <c r="C239" s="3" t="n">
-        <v>-0.04795435230706814</v>
+        <v>-0.04795435230706337</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>0.06163890684207545</v>
+        <v>0.06163890684207764</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>0.436575872854789</v>
+        <v>0.4365758728548509</v>
       </c>
       <c r="F239" s="3" t="inlineStr"/>
       <c r="G239" s="3" t="n">
-        <v>-0.7779883642312412</v>
+        <v>-0.7779883642311363</v>
       </c>
     </row>
     <row r="240">
@@ -16702,50 +16702,46 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Poverty Gap Squared</t>
+          <t>Poverty Gap ($4.20/day)</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
-        <v>5.894749998078418e-05</v>
+        <v>-0.001307639327058881</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>6.885937413131019e-05</v>
+        <v>0.003636871287130495</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>0.3919666473886876</v>
+        <v>0.7191832164455461</v>
       </c>
       <c r="F240" s="3" t="inlineStr"/>
       <c r="G240" s="3" t="n">
-        <v>0.8560562846298206</v>
+        <v>-0.3595506202504662</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="4" t="inlineStr">
+      <c r="A241" s="3" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.BQCI</t>
         </is>
       </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>Building Quality Index</t>
-        </is>
-      </c>
-      <c r="C241" s="4" t="n">
-        <v>0.00982022055073203</v>
-      </c>
-      <c r="D241" s="4" t="n">
-        <v>0.005504401161288257</v>
-      </c>
-      <c r="E241" s="4" t="n">
-        <v>0.07441277628526662</v>
-      </c>
-      <c r="F241" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G241" s="4" t="n">
-        <v>1.784067015281585</v>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Poverty Gap Squared</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>5.894749998074606e-05</v>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>6.885937413131573e-05</v>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>0.391966647389032</v>
+      </c>
+      <c r="F241" s="3" t="inlineStr"/>
+      <c r="G241" s="3" t="n">
+        <v>0.856056284629198</v>
       </c>
     </row>
     <row r="242">
@@ -16756,100 +16752,104 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Storm Count (Log)</t>
+          <t>Flood Count (Log)</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
-        <v>-0.003813241440898606</v>
+        <v>-0.02616587541410692</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>0.01434378692808925</v>
+        <v>0.01919255060576682</v>
       </c>
       <c r="E242" s="3" t="n">
-        <v>0.7903576502553388</v>
+        <v>0.172776965511807</v>
       </c>
       <c r="F242" s="3" t="inlineStr"/>
       <c r="G242" s="3" t="n">
-        <v>-0.2658462134174056</v>
+        <v>-1.363334970509069</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="4" t="inlineStr">
+      <c r="A243" s="3" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.BQCI</t>
         </is>
       </c>
-      <c r="B243" s="4" t="inlineStr">
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>Storm Count (Log)</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>-0.00381324144089863</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>0.0143437869280893</v>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>0.7903576502553382</v>
+      </c>
+      <c r="F243" s="3" t="inlineStr"/>
+      <c r="G243" s="3" t="n">
+        <v>-0.2658462134174063</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>ONLY-J+K+N.Int.BQCI</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
         <is>
           <t>Log GDP per Capita (PPP)</t>
         </is>
       </c>
-      <c r="C243" s="4" t="n">
-        <v>0.05494914979059932</v>
-      </c>
-      <c r="D243" s="4" t="n">
-        <v>0.0306314476819133</v>
-      </c>
-      <c r="E243" s="4" t="n">
-        <v>0.07283228043607802</v>
-      </c>
-      <c r="F243" s="4" t="inlineStr">
+      <c r="C244" s="4" t="n">
+        <v>0.05494914979059916</v>
+      </c>
+      <c r="D244" s="4" t="n">
+        <v>0.03063144768191336</v>
+      </c>
+      <c r="E244" s="4" t="n">
+        <v>0.07283228043607949</v>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
-        <v>1.79388027497782</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="3" t="inlineStr">
+      <c r="G244" s="4" t="n">
+        <v>1.79388027497781</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
         <is>
           <t>ONLY-J+K+N.Int.BQCI</t>
         </is>
       </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>Flood Count (Log)</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="n">
-        <v>-0.02616587541410705</v>
-      </c>
-      <c r="D244" s="3" t="n">
-        <v>0.01919255060576678</v>
-      </c>
-      <c r="E244" s="3" t="n">
-        <v>0.1727769655118041</v>
-      </c>
-      <c r="F244" s="3" t="inlineStr"/>
-      <c r="G244" s="3" t="n">
-        <v>-1.363334970509078</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="3" t="inlineStr">
-        <is>
-          <t>ONLY-J+K+N.Int.BQCI</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="inlineStr">
-        <is>
-          <t>Earthquake Count (Log)</t>
-        </is>
-      </c>
-      <c r="C245" s="3" t="n">
-        <v>0.03181460469396809</v>
-      </c>
-      <c r="D245" s="3" t="n">
-        <v>0.02319731194699326</v>
-      </c>
-      <c r="E245" s="3" t="n">
-        <v>0.17022597419911</v>
-      </c>
-      <c r="F245" s="3" t="inlineStr"/>
-      <c r="G245" s="3" t="n">
-        <v>1.371478073264078</v>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="n">
+        <v>0.001932112782203798</v>
+      </c>
+      <c r="D245" s="4" t="n">
+        <v>0.001075831285440528</v>
+      </c>
+      <c r="E245" s="4" t="n">
+        <v>0.07250637473506542</v>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="n">
+        <v>1.795925447002262</v>
       </c>
     </row>
     <row r="246">
@@ -16860,21 +16860,21 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Poverty Gap ($4.20/day)</t>
+          <t>Earthquake Count (Log)</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
-        <v>-0.001307639327059395</v>
+        <v>0.03181460469396821</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>0.003636871287130431</v>
+        <v>0.02319731194699327</v>
       </c>
       <c r="E246" s="3" t="n">
-        <v>0.7191832164454357</v>
+        <v>0.1702259741991089</v>
       </c>
       <c r="F246" s="3" t="inlineStr"/>
       <c r="G246" s="3" t="n">
-        <v>-0.3595506202506138</v>
+        <v>1.371478073264082</v>
       </c>
     </row>
     <row r="247">
@@ -16885,17 +16885,17 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Urban Population %</t>
+          <t>Building Quality Index</t>
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>0.001932112782203869</v>
+        <v>0.009820220550732204</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>0.001075831285440526</v>
+        <v>0.005504401161288286</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>0.07250637473505435</v>
+        <v>0.07441277628526299</v>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="G247" s="4" t="n">
-        <v>1.795925447002331</v>
+        <v>1.784067015281607</v>
       </c>
     </row>
     <row r="248">
@@ -16918,17 +16918,17 @@
         </is>
       </c>
       <c r="C248" s="3" t="n">
-        <v>0.007341580450700833</v>
+        <v>0.007341580450700753</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>0.008039606495731138</v>
+        <v>0.00803960649573114</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>0.3611496736074523</v>
+        <v>0.3611496736074575</v>
       </c>
       <c r="F248" s="3" t="inlineStr"/>
       <c r="G248" s="3" t="n">
-        <v>0.9131765907447159</v>
+        <v>0.9131765907447058</v>
       </c>
     </row>
     <row r="249">
@@ -16943,17 +16943,17 @@
         </is>
       </c>
       <c r="C249" s="3" t="n">
-        <v>-0.002741430704651762</v>
+        <v>-0.002741430704651778</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>0.004476396422359714</v>
+        <v>0.004476396422359728</v>
       </c>
       <c r="E249" s="3" t="n">
-        <v>0.5402605026503001</v>
+        <v>0.5402605026502989</v>
       </c>
       <c r="F249" s="3" t="inlineStr"/>
       <c r="G249" s="3" t="n">
-        <v>-0.6124191081375738</v>
+        <v>-0.6124191081375755</v>
       </c>
     </row>
     <row r="250">
@@ -16968,17 +16968,17 @@
         </is>
       </c>
       <c r="C250" s="3" t="n">
-        <v>-0.004384017748326646</v>
+        <v>-0.00438401774832656</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>0.00569910670504275</v>
+        <v>0.005699106705042749</v>
       </c>
       <c r="E250" s="3" t="n">
-        <v>0.4417470049642086</v>
+        <v>0.4417470049642174</v>
       </c>
       <c r="F250" s="3" t="inlineStr"/>
       <c r="G250" s="3" t="n">
-        <v>-0.7692464758463863</v>
+        <v>-0.7692464758463714</v>
       </c>
     </row>
     <row r="251">
@@ -16993,7 +16993,7 @@
         </is>
       </c>
       <c r="C251" s="3" t="n">
-        <v>0.6329988805329078</v>
+        <v>0.6329988805329076</v>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr"/>
@@ -17012,7 +17012,7 @@
         </is>
       </c>
       <c r="C252" s="3" t="n">
-        <v>0.585733584843964</v>
+        <v>0.5857335848439639</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr"/>
@@ -18963,13 +18963,13 @@
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>0.2697066017500969</v>
+        <v>0.2697066017500954</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>0.0502134225363474</v>
+        <v>0.05021342253634842</v>
       </c>
       <c r="E329" s="2" t="n">
-        <v>7.821209969367995e-08</v>
+        <v>7.821209969373992e-08</v>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         </is>
       </c>
       <c r="G329" s="2" t="n">
-        <v>5.371205309792765</v>
+        <v>5.371205309792627</v>
       </c>
     </row>
     <row r="330">
@@ -18992,17 +18992,17 @@
         </is>
       </c>
       <c r="C330" s="3" t="n">
-        <v>0.102931650935831</v>
+        <v>0.1029316509358299</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>0.06713800651741017</v>
+        <v>0.0671380065174097</v>
       </c>
       <c r="E330" s="3" t="n">
-        <v>0.1252425100342528</v>
+        <v>0.1252425100342542</v>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
       <c r="G330" s="3" t="n">
-        <v>1.53313534725132</v>
+        <v>1.533135347251314</v>
       </c>
     </row>
     <row r="331">
@@ -19017,13 +19017,13 @@
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>-0.1932682782453445</v>
+        <v>-0.1932682782453462</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>0.05852298963632414</v>
+        <v>0.05852298963632406</v>
       </c>
       <c r="E331" s="2" t="n">
-        <v>0.0009584983128488253</v>
+        <v>0.0009584983128487068</v>
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         </is>
       </c>
       <c r="G331" s="2" t="n">
-        <v>-3.302433444469598</v>
+        <v>-3.302433444469632</v>
       </c>
     </row>
     <row r="332">
@@ -19049,10 +19049,10 @@
         <v>0.1994600462431011</v>
       </c>
       <c r="D332" s="5" t="n">
-        <v>0.08713383385221983</v>
+        <v>0.08713383385221946</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>0.02207221809219082</v>
+        <v>0.02207221809219026</v>
       </c>
       <c r="F332" s="5" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2.289122805974405</v>
+        <v>2.289122805974415</v>
       </c>
     </row>
     <row r="333">
@@ -19075,13 +19075,13 @@
         </is>
       </c>
       <c r="C333" s="2" t="n">
-        <v>-0.3709096462168471</v>
+        <v>-0.3709096462168474</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>0.08296153279465328</v>
+        <v>0.08296153279465175</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>7.790459835852104e-06</v>
+        <v>7.790459835849038e-06</v>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         </is>
       </c>
       <c r="G333" s="2" t="n">
-        <v>-4.470862985799988</v>
+        <v>-4.470862985800072</v>
       </c>
     </row>
     <row r="334">
@@ -19104,17 +19104,17 @@
         </is>
       </c>
       <c r="C334" s="3" t="n">
-        <v>0.1131133019521266</v>
+        <v>0.1131133019521263</v>
       </c>
       <c r="D334" s="3" t="n">
-        <v>0.1137630808147855</v>
+        <v>0.1137630808147852</v>
       </c>
       <c r="E334" s="3" t="n">
         <v>0.320082522746063</v>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
       <c r="G334" s="3" t="n">
-        <v>0.9942883151721534</v>
+        <v>0.9942883151721535</v>
       </c>
     </row>
     <row r="335">
@@ -19129,17 +19129,17 @@
         </is>
       </c>
       <c r="C335" s="3" t="n">
-        <v>-0.0539043717200192</v>
+        <v>-0.05390437172002108</v>
       </c>
       <c r="D335" s="3" t="n">
-        <v>0.05266124366785415</v>
+        <v>0.05266124366785346</v>
       </c>
       <c r="E335" s="3" t="n">
-        <v>0.3060213496792776</v>
+        <v>0.3060213496792544</v>
       </c>
       <c r="F335" s="3" t="inlineStr"/>
       <c r="G335" s="3" t="n">
-        <v>-1.023606127876617</v>
+        <v>-1.023606127876666</v>
       </c>
     </row>
     <row r="336">
@@ -19150,21 +19150,21 @@
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>3 Hazards Combined (Log)</t>
+          <t>Poverty Gap ($4.20/day)</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
-        <v>0.01135115523694769</v>
+        <v>-0.002098265121421898</v>
       </c>
       <c r="D336" s="3" t="n">
-        <v>0.01597696999981691</v>
+        <v>0.003304591605203861</v>
       </c>
       <c r="E336" s="3" t="n">
-        <v>0.4774128305345863</v>
+        <v>0.525458127827179</v>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
       <c r="G336" s="3" t="n">
-        <v>0.7104698348358773</v>
+        <v>-0.6349544428175885</v>
       </c>
     </row>
     <row r="337">
@@ -19179,17 +19179,17 @@
         </is>
       </c>
       <c r="C337" s="3" t="n">
-        <v>3.467898059736764e-05</v>
+        <v>3.467898059738235e-05</v>
       </c>
       <c r="D337" s="3" t="n">
-        <v>6.348366309379133e-05</v>
+        <v>6.348366309378835e-05</v>
       </c>
       <c r="E337" s="3" t="n">
-        <v>0.5848829535788385</v>
+        <v>0.5848829535786617</v>
       </c>
       <c r="F337" s="3" t="inlineStr"/>
       <c r="G337" s="3" t="n">
-        <v>0.5462662188559064</v>
+        <v>0.5462662188561637</v>
       </c>
     </row>
     <row r="338">
@@ -19204,13 +19204,13 @@
         </is>
       </c>
       <c r="C338" s="5" t="n">
-        <v>0.06177644053127315</v>
+        <v>0.06177644053127362</v>
       </c>
       <c r="D338" s="5" t="n">
-        <v>0.03038261816653511</v>
+        <v>0.03038261816653514</v>
       </c>
       <c r="E338" s="5" t="n">
-        <v>0.04202400775069289</v>
+        <v>0.04202400775069152</v>
       </c>
       <c r="F338" s="5" t="inlineStr">
         <is>
@@ -19218,61 +19218,61 @@
         </is>
       </c>
       <c r="G338" s="5" t="n">
-        <v>2.033282325856852</v>
+        <v>2.033282325856865</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="3" t="inlineStr">
+      <c r="A339" s="4" t="inlineStr">
         <is>
           <t>ONLY-M.Int.Pov</t>
         </is>
       </c>
-      <c r="B339" s="3" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C339" s="3" t="n">
-        <v>-0.002098265121421682</v>
-      </c>
-      <c r="D339" s="3" t="n">
-        <v>0.003304591605203886</v>
-      </c>
-      <c r="E339" s="3" t="n">
-        <v>0.525458127827225</v>
-      </c>
-      <c r="F339" s="3" t="inlineStr"/>
-      <c r="G339" s="3" t="n">
-        <v>-0.6349544428175182</v>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="n">
+        <v>0.001830130320574808</v>
+      </c>
+      <c r="D339" s="4" t="n">
+        <v>0.001011872334961565</v>
+      </c>
+      <c r="E339" s="4" t="n">
+        <v>0.07050425516332505</v>
+      </c>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G339" s="4" t="n">
+        <v>1.808657334864605</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="4" t="inlineStr">
+      <c r="A340" s="3" t="inlineStr">
         <is>
           <t>ONLY-M.Int.Pov</t>
         </is>
       </c>
-      <c r="B340" s="4" t="inlineStr">
-        <is>
-          <t>Urban Population %</t>
-        </is>
-      </c>
-      <c r="C340" s="4" t="n">
-        <v>0.00183013032057481</v>
-      </c>
-      <c r="D340" s="4" t="n">
-        <v>0.001011872334961567</v>
-      </c>
-      <c r="E340" s="4" t="n">
-        <v>0.07050425516332552</v>
-      </c>
-      <c r="F340" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G340" s="4" t="n">
-        <v>1.808657334864602</v>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>3 Hazards Combined (Log)</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="n">
+        <v>0.01135115523694783</v>
+      </c>
+      <c r="D340" s="3" t="n">
+        <v>0.01597696999981685</v>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>0.4774128305345792</v>
+      </c>
+      <c r="F340" s="3" t="inlineStr"/>
+      <c r="G340" s="3" t="n">
+        <v>0.7104698348358885</v>
       </c>
     </row>
     <row r="341">
@@ -19287,13 +19287,13 @@
         </is>
       </c>
       <c r="C341" s="4" t="n">
-        <v>0.002323419376797336</v>
+        <v>0.00232341937679738</v>
       </c>
       <c r="D341" s="4" t="n">
-        <v>0.001380841921433632</v>
+        <v>0.001380841921433629</v>
       </c>
       <c r="E341" s="4" t="n">
-        <v>0.0924504810966766</v>
+        <v>0.09245048109666981</v>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         </is>
       </c>
       <c r="G341" s="4" t="n">
-        <v>1.682610688981032</v>
+        <v>1.682610688981068</v>
       </c>
     </row>
     <row r="342">
@@ -19316,7 +19316,7 @@
         </is>
       </c>
       <c r="C342" s="3" t="n">
-        <v>0.6101923611425208</v>
+        <v>0.610192361142521</v>
       </c>
       <c r="D342" s="3" t="inlineStr"/>
       <c r="E342" s="3" t="inlineStr"/>
@@ -19335,7 +19335,7 @@
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>0.5760486263520848</v>
+        <v>0.5760486263520849</v>
       </c>
       <c r="D343" s="3" t="inlineStr"/>
       <c r="E343" s="3" t="inlineStr"/>
@@ -19373,13 +19373,13 @@
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>0.267392337002886</v>
+        <v>0.2673923370028872</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>0.0496720788571527</v>
+        <v>0.04967207885715236</v>
       </c>
       <c r="E345" s="2" t="n">
-        <v>7.31927917334713e-08</v>
+        <v>7.319279173344647e-08</v>
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         </is>
       </c>
       <c r="G345" s="2" t="n">
-        <v>5.383151725375833</v>
+        <v>5.383151725375893</v>
       </c>
     </row>
     <row r="346">
@@ -19402,17 +19402,17 @@
         </is>
       </c>
       <c r="C346" s="3" t="n">
-        <v>0.1016099901851877</v>
+        <v>0.1016099901851888</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>0.06586563699256043</v>
+        <v>0.06586563699256077</v>
       </c>
       <c r="E346" s="3" t="n">
-        <v>0.1229070020187095</v>
+        <v>0.1229070020187075</v>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
       <c r="G346" s="3" t="n">
-        <v>1.542685910661801</v>
+        <v>1.54268591066181</v>
       </c>
     </row>
     <row r="347">
@@ -19427,13 +19427,13 @@
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>-0.1984694940678861</v>
+        <v>-0.1984694940678854</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>0.05838038053724581</v>
+        <v>0.05838038053724649</v>
       </c>
       <c r="E347" s="2" t="n">
-        <v>0.0006748638982774421</v>
+        <v>0.0006748638982775735</v>
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         </is>
       </c>
       <c r="G347" s="2" t="n">
-        <v>-3.399592332928792</v>
+        <v>-3.399592332928739</v>
       </c>
     </row>
     <row r="348">
@@ -19456,13 +19456,13 @@
         </is>
       </c>
       <c r="C348" s="5" t="n">
-        <v>0.1901385928793792</v>
+        <v>0.1901385928793786</v>
       </c>
       <c r="D348" s="5" t="n">
-        <v>0.087045588047253</v>
+        <v>0.08704558804725347</v>
       </c>
       <c r="E348" s="5" t="n">
-        <v>0.02893606471491279</v>
+        <v>0.02893606471491413</v>
       </c>
       <c r="F348" s="5" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         </is>
       </c>
       <c r="G348" s="5" t="n">
-        <v>2.184356463605735</v>
+        <v>2.184356463605717</v>
       </c>
     </row>
     <row r="349">
@@ -19485,13 +19485,13 @@
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>-0.3233428173570845</v>
+        <v>-0.3233428173570817</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>0.09388790303335044</v>
+        <v>0.093887903033352</v>
       </c>
       <c r="E349" s="2" t="n">
-        <v>0.000573336505980135</v>
+        <v>0.0005733365059803187</v>
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="G349" s="2" t="n">
-        <v>-3.4439241575374</v>
+        <v>-3.443924157537313</v>
       </c>
     </row>
     <row r="350">
@@ -19514,17 +19514,17 @@
         </is>
       </c>
       <c r="C350" s="3" t="n">
-        <v>0.08525380175570584</v>
+        <v>0.08525380175570743</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>0.1280053421491435</v>
+        <v>0.1280053421491436</v>
       </c>
       <c r="E350" s="3" t="n">
-        <v>0.5053998958896374</v>
+        <v>0.5053998958896297</v>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
       <c r="G350" s="3" t="n">
-        <v>0.6660175296150814</v>
+        <v>0.6660175296150936</v>
       </c>
     </row>
     <row r="351">
@@ -19539,17 +19539,17 @@
         </is>
       </c>
       <c r="C351" s="3" t="n">
-        <v>-0.05296205665849797</v>
+        <v>-0.05296205665850593</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>0.05159276035856414</v>
+        <v>0.05159276035856159</v>
       </c>
       <c r="E351" s="3" t="n">
-        <v>0.3046368960457582</v>
+        <v>0.3046368960456617</v>
       </c>
       <c r="F351" s="3" t="inlineStr"/>
       <c r="G351" s="3" t="n">
-        <v>-1.026540473710214</v>
+        <v>-1.026540473710419</v>
       </c>
     </row>
     <row r="352">
@@ -19560,21 +19560,21 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>3 Hazards Combined (Log)</t>
+          <t>Poverty Gap ($4.20/day)</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
-        <v>0.01057461863589614</v>
+        <v>-0.003265677138616213</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>0.01834507448931486</v>
+        <v>0.003267711199540781</v>
       </c>
       <c r="E352" s="3" t="n">
-        <v>0.5643257744023551</v>
+        <v>0.3176118419471425</v>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
       <c r="G352" s="3" t="n">
-        <v>0.57642822012281</v>
+        <v>-0.9993775273271234</v>
       </c>
     </row>
     <row r="353">
@@ -19589,17 +19589,17 @@
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>6.885077979355675e-05</v>
+        <v>6.885077979354973e-05</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>6.21349675464946e-05</v>
+        <v>6.213496754649197e-05</v>
       </c>
       <c r="E353" s="3" t="n">
-        <v>0.2678254261613601</v>
+        <v>0.2678254261613886</v>
       </c>
       <c r="F353" s="3" t="inlineStr"/>
       <c r="G353" s="3" t="n">
-        <v>1.108084264179213</v>
+        <v>1.108084264179147</v>
       </c>
     </row>
     <row r="354">
@@ -19614,13 +19614,13 @@
         </is>
       </c>
       <c r="C354" s="4" t="n">
-        <v>0.04984626388727724</v>
+        <v>0.04984626388727702</v>
       </c>
       <c r="D354" s="4" t="n">
-        <v>0.02976941765308121</v>
+        <v>0.02976941765308111</v>
       </c>
       <c r="E354" s="4" t="n">
-        <v>0.09404969735914386</v>
+        <v>0.09404969735914417</v>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
@@ -19628,61 +19628,61 @@
         </is>
       </c>
       <c r="G354" s="4" t="n">
-        <v>1.67441178958091</v>
+        <v>1.674411789580908</v>
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="3" t="inlineStr">
+      <c r="A355" s="4" t="inlineStr">
         <is>
           <t>ONLY-M.Int.GDP</t>
         </is>
       </c>
-      <c r="B355" s="3" t="inlineStr">
-        <is>
-          <t>Poverty Gap ($4.20/day)</t>
-        </is>
-      </c>
-      <c r="C355" s="3" t="n">
-        <v>-0.003265677138616438</v>
-      </c>
-      <c r="D355" s="3" t="n">
-        <v>0.003267711199540755</v>
-      </c>
-      <c r="E355" s="3" t="n">
-        <v>0.3176118419471055</v>
-      </c>
-      <c r="F355" s="3" t="inlineStr"/>
-      <c r="G355" s="3" t="n">
-        <v>-0.9993775273271999</v>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>Urban Population %</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="n">
+        <v>0.001969515451419227</v>
+      </c>
+      <c r="D355" s="4" t="n">
+        <v>0.001013805596789512</v>
+      </c>
+      <c r="E355" s="4" t="n">
+        <v>0.05205297450554305</v>
+      </c>
+      <c r="F355" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G355" s="4" t="n">
+        <v>1.942695382286533</v>
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="4" t="inlineStr">
+      <c r="A356" s="3" t="inlineStr">
         <is>
           <t>ONLY-M.Int.GDP</t>
         </is>
       </c>
-      <c r="B356" s="4" t="inlineStr">
-        <is>
-          <t>Urban Population %</t>
-        </is>
-      </c>
-      <c r="C356" s="4" t="n">
-        <v>0.001969515451419161</v>
-      </c>
-      <c r="D356" s="4" t="n">
-        <v>0.00101380559678951</v>
-      </c>
-      <c r="E356" s="4" t="n">
-        <v>0.05205297450555053</v>
-      </c>
-      <c r="F356" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G356" s="4" t="n">
-        <v>1.942695382286471</v>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>3 Hazards Combined (Log)</t>
+        </is>
+      </c>
+      <c r="C356" s="3" t="n">
+        <v>0.01057461863589507</v>
+      </c>
+      <c r="D356" s="3" t="n">
+        <v>0.01834507448931489</v>
+      </c>
+      <c r="E356" s="3" t="n">
+        <v>0.5643257744023951</v>
+      </c>
+      <c r="F356" s="3" t="inlineStr"/>
+      <c r="G356" s="3" t="n">
+        <v>0.5764282201227509</v>
       </c>
     </row>
     <row r="357">
@@ -19697,17 +19697,17 @@
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>-0.02282027671666368</v>
+        <v>-0.02282027671666352</v>
       </c>
       <c r="D357" s="3" t="n">
         <v>0.0182050641576721</v>
       </c>
       <c r="E357" s="3" t="n">
-        <v>0.2100192282406749</v>
+        <v>0.2100192282406782</v>
       </c>
       <c r="F357" s="3" t="inlineStr"/>
       <c r="G357" s="3" t="n">
-        <v>-1.253512567658082</v>
+        <v>-1.253512567658073</v>
       </c>
     </row>
     <row r="358">
@@ -19779,13 +19779,13 @@
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>0.2585709479620591</v>
+        <v>0.258570947962059</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>0.04948551791036762</v>
+        <v>0.04948551791036749</v>
       </c>
       <c r="E361" s="2" t="n">
-        <v>1.739817915461259e-07</v>
+        <v>1.739817915461159e-07</v>
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         </is>
       </c>
       <c r="G361" s="2" t="n">
-        <v>5.225184233302455</v>
+        <v>5.225184233302466</v>
       </c>
     </row>
     <row r="362">
@@ -19808,17 +19808,17 @@
         </is>
       </c>
       <c r="C362" s="3" t="n">
-        <v>0.1075148760393786</v>
+        <v>0.1075148760393809</v>
       </c>
       <c r="D362" s="3" t="n">
-        <v>0.06563721165543247</v>
+        <v>0.06563721165543385</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>0.1014181236653887</v>
+        <v>0.1014181236653883</v>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
       <c r="G362" s="3" t="n">
-        <v>1.638017114495754</v>
+        <v>1.638017114495756</v>
       </c>
     </row>
     <row r="363">
@@ -19833,13 +19833,13 @@
         </is>
       </c>
       <c r="C363" s="2" t="n">
-        <v>-0.1892967646663603</v>
+        <v>-0.189296764666356</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>0.05896504834288271</v>
+        <v>0.05896504834288407</v>
       </c>
       <c r="E363" s="2" t="n">
-        <v>0.001325865698772687</v>
+        <v>0.001325865698773366</v>
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         </is>
       </c>
       <c r="G363" s="2" t="n">
-        <v>-3.210321537694611</v>
+        <v>-3.210321537694464</v>
       </c>
     </row>
     <row r="364">
@@ -19862,13 +19862,13 @@
         </is>
       </c>
       <c r="C364" s="5" t="n">
-        <v>0.2053485014478138</v>
+        <v>0.2053485014478162</v>
       </c>
       <c r="D364" s="5" t="n">
-        <v>0.09019261044012421</v>
+        <v>0.09019261044012442</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>0.02279951888107542</v>
+        <v>0.02279951888107412</v>
       </c>
       <c r="F364" s="5" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         </is>
       </c>
       <c r="G364" s="5" t="n">
-        <v>2.276777448238264</v>
+        <v>2.276777448238286</v>
       </c>
     </row>
     <row r="365">
@@ -19891,13 +19891,13 @@
         </is>
       </c>
       <c r="C365" s="2" t="n">
-        <v>-0.3441480151448922</v>
+        <v>-0.3441480151448847</v>
       </c>
       <c r="D365" s="2" t="n">
-        <v>0.08957237139745709</v>
+        <v>0.0895723713974593</v>
       </c>
       <c r="E365" s="2" t="n">
-        <v>0.0001219749752248714</v>
+        <v>0.0001219749752249601</v>
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         </is>
       </c>
       <c r="G365" s="2" t="n">
-        <v>-3.842122406448451</v>
+        <v>-3.842122406448272</v>
       </c>
     </row>
     <row r="366">
@@ -19920,17 +19920,17 @@
         </is>
       </c>
       <c r="C366" s="3" t="n">
-        <v>0.1021593143017229</v>
+        <v>0.1021593143017224</v>
       </c>
       <c r="D366" s="3" t="n">
-        <v>0.118690437171449</v>
+        <v>0.1186904371714492</v>
       </c>
       <c r="E366" s="3" t="n">
-        <v>0.3893918981380726</v>
+        <v>0.389391898138076</v>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
       <c r="G366" s="3" t="n">
-        <v>0.8607206842970275</v>
+        <v>0.8607206842970216</v>
       </c>
     </row>
     <row r="367">
@@ -19945,17 +19945,17 @@
         </is>
       </c>
       <c r="C367" s="3" t="n">
-        <v>-0.04404046049108298</v>
+        <v>-0.04404046049108652</v>
       </c>
       <c r="D367" s="3" t="n">
-        <v>0.05233565409988891</v>
+        <v>0.0523356540998875</v>
       </c>
       <c r="E367" s="3" t="n">
-        <v>0.4000678040758489</v>
+        <v>0.4000678040757982</v>
       </c>
       <c r="F367" s="3" t="inlineStr"/>
       <c r="G367" s="3" t="n">
-        <v>-0.841500144567343</v>
+        <v>-0.8415001445674334</v>
       </c>
     </row>
     <row r="368">
@@ -19966,21 +19966,21 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>3 Hazards Combined (Log)</t>
+          <t>Poverty Gap ($4.20/day)</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
-        <v>0.009345726870067654</v>
+        <v>-0.003243244677978613</v>
       </c>
       <c r="D368" s="3" t="n">
-        <v>0.01703557052270633</v>
+        <v>0.003282813395010347</v>
       </c>
       <c r="E368" s="3" t="n">
-        <v>0.5832794668178582</v>
+        <v>0.323178749842948</v>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
       <c r="G368" s="3" t="n">
-        <v>0.548600756142035</v>
+        <v>-0.9879467053802461</v>
       </c>
     </row>
     <row r="369">
@@ -19991,21 +19991,21 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>Poverty Gap Squared</t>
+          <t>Government Effectiveness (WGI)</t>
         </is>
       </c>
       <c r="C369" s="3" t="n">
-        <v>7.996844832025651e-05</v>
+        <v>0.0113656783936025</v>
       </c>
       <c r="D369" s="3" t="n">
-        <v>6.154533633871882e-05</v>
+        <v>0.01998544142787653</v>
       </c>
       <c r="E369" s="3" t="n">
-        <v>0.1938265426107257</v>
+        <v>0.56956117920668</v>
       </c>
       <c r="F369" s="3" t="inlineStr"/>
       <c r="G369" s="3" t="n">
-        <v>1.299342128543175</v>
+        <v>0.5686978911433591</v>
       </c>
     </row>
     <row r="370">
@@ -20016,21 +20016,21 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>Log GDP per Capita (PPP)</t>
+          <t>Poverty Gap Squared</t>
         </is>
       </c>
       <c r="C370" s="3" t="n">
-        <v>0.04701110085133706</v>
+        <v>7.996844832025855e-05</v>
       </c>
       <c r="D370" s="3" t="n">
-        <v>0.03115553322851057</v>
+        <v>6.154533633872046e-05</v>
       </c>
       <c r="E370" s="3" t="n">
-        <v>0.1313201005460237</v>
+        <v>0.1938265426107263</v>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
       <c r="G370" s="3" t="n">
-        <v>1.508916586550892</v>
+        <v>1.299342128543173</v>
       </c>
     </row>
     <row r="371">
@@ -20041,21 +20041,21 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>Poverty Gap ($4.20/day)</t>
+          <t>Log GDP per Capita (PPP)</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
-        <v>-0.003243244677978901</v>
+        <v>0.04701110085133817</v>
       </c>
       <c r="D371" s="3" t="n">
-        <v>0.003282813395010327</v>
+        <v>0.03115553322851047</v>
       </c>
       <c r="E371" s="3" t="n">
-        <v>0.3231787498429021</v>
+        <v>0.1313201005460133</v>
       </c>
       <c r="F371" s="3" t="inlineStr"/>
       <c r="G371" s="3" t="n">
-        <v>-0.9879467053803399</v>
+        <v>1.508916586550932</v>
       </c>
     </row>
     <row r="372">
@@ -20070,13 +20070,13 @@
         </is>
       </c>
       <c r="C372" s="4" t="n">
-        <v>0.001830606500532256</v>
+        <v>0.001830606500532164</v>
       </c>
       <c r="D372" s="4" t="n">
-        <v>0.001019593031106156</v>
+        <v>0.001019593031106148</v>
       </c>
       <c r="E372" s="4" t="n">
-        <v>0.07258543725072288</v>
+        <v>0.07258543725073488</v>
       </c>
       <c r="F372" s="4" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         </is>
       </c>
       <c r="G372" s="4" t="n">
-        <v>1.795428611890601</v>
+        <v>1.795428611890526</v>
       </c>
     </row>
     <row r="373">
@@ -20095,21 +20095,21 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>Government Effectiveness (WGI)</t>
+          <t>3 Hazards Combined (Log)</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
-        <v>0.01136567839360362</v>
+        <v>0.009345726870068256</v>
       </c>
       <c r="D373" s="3" t="n">
-        <v>0.01998544142787655</v>
+        <v>0.01703557052270634</v>
       </c>
       <c r="E373" s="3" t="n">
-        <v>0.5695611792066424</v>
+        <v>0.5832794668178343</v>
       </c>
       <c r="F373" s="3" t="inlineStr"/>
       <c r="G373" s="3" t="n">
-        <v>0.5686978911434146</v>
+        <v>0.54860075614207</v>
       </c>
     </row>
     <row r="374">
@@ -20124,17 +20124,17 @@
         </is>
       </c>
       <c r="C374" s="3" t="n">
-        <v>-0.01952059068745479</v>
+        <v>-0.01952059068745501</v>
       </c>
       <c r="D374" s="3" t="n">
-        <v>0.01756126786824566</v>
+        <v>0.01756126786824564</v>
       </c>
       <c r="E374" s="3" t="n">
-        <v>0.2663227793569813</v>
+        <v>0.2663227793569757</v>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
       <c r="G374" s="3" t="n">
-        <v>-1.111570692612234</v>
+        <v>-1.111570692612247</v>
       </c>
     </row>
     <row r="375">
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="C375" s="3" t="n">
-        <v>0.6114705110485419</v>
+        <v>0.6114705110485418</v>
       </c>
       <c r="D375" s="3" t="inlineStr"/>
       <c r="E375" s="3" t="inlineStr"/>
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="C376" s="3" t="n">
-        <v>0.5743316628399466</v>
+        <v>0.5743316628399464</v>
       </c>
       <c r="D376" s="3" t="inlineStr"/>
       <c r="E376" s="3" t="inlineStr"/>
@@ -20206,13 +20206,13 @@
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>0.2840864753199224</v>
+        <v>0.2840864753199238</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>0.05483234525359709</v>
+        <v>0.05483234525359622</v>
       </c>
       <c r="E378" s="2" t="n">
-        <v>2.206974516555228e-07</v>
+        <v>2.206974516553953e-07</v>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G378" s="2" t="n">
-        <v>5.181001724548446</v>
+        <v>5.181001724548554</v>
       </c>
     </row>
     <row r="379">
@@ -20235,17 +20235,17 @@
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>0.08580134322396786</v>
+        <v>0.0858013432239685</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>0.07031687469594056</v>
+        <v>0.07031687469594115</v>
       </c>
       <c r="E379" s="3" t="n">
-        <v>0.2223853332828514</v>
+        <v>0.2223853332828517</v>
       </c>
       <c r="F379" s="3" t="inlineStr"/>
       <c r="G379" s="3" t="n">
-        <v>1.220209851404577</v>
+        <v>1.220209851404575</v>
       </c>
     </row>
     <row r="380">
@@ -20260,13 +20260,13 @@
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>-0.1847406295317233</v>
+        <v>-0.1847406295317225</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>0.05809433240937515</v>
+        <v>0.0580943324093752</v>
       </c>
       <c r="E380" s="2" t="n">
-        <v>0.001472693443724913</v>
+        <v>0.001472693443725</v>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         </is>
       </c>
       <c r="G380" s="2" t="n">
-        <v>-3.180011231214531</v>
+        <v>-3.180011231214514</v>
       </c>
     </row>
     <row r="381">
@@ -20289,13 +20289,13 @@
         </is>
       </c>
       <c r="C381" s="4" t="n">
-        <v>0.1546136663803598</v>
+        <v>0.1546136663803603</v>
       </c>
       <c r="D381" s="4" t="n">
-        <v>0.09016733071781825</v>
+        <v>0.09016733071781824</v>
       </c>
       <c r="E381" s="4" t="n">
-        <v>0.08639262626284028</v>
+        <v>0.08639262626283918</v>
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="G381" s="4" t="n">
-        <v>1.714741527219305</v>
+        <v>1.714741527219311</v>
       </c>
     </row>
     <row r="382">
@@ -20318,13 +20318,13 @@
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>-0.384391157489305</v>
+        <v>-0.3843911574893011</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>0.08256670711938481</v>
+        <v>0.08256670711938503</v>
       </c>
       <c r="E382" s="2" t="n">
-        <v>3.231602110964826e-06</v>
+        <v>3.231602110965766e-06</v>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G382" s="2" t="n">
-        <v>-4.655522436343578</v>
+        <v>-4.655522436343518</v>
       </c>
     </row>
     <row r="383">
@@ -20347,13 +20347,13 @@
         </is>
       </c>
       <c r="C383" s="3" t="n">
-        <v>0.1097622295873287</v>
+        <v>0.109762229587329</v>
       </c>
       <c r="D383" s="3" t="n">
-        <v>0.1072735931064706</v>
+        <v>0.1072735931064709</v>
       </c>
       <c r="E383" s="3" t="n">
-        <v>0.306213781544508</v>
+        <v>0.3062137815445083</v>
       </c>
       <c r="F383" s="3" t="inlineStr"/>
       <c r="G383" s="3" t="n">
@@ -20372,17 +20372,17 @@
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>-0.0790747643539971</v>
+        <v>-0.07907476435399656</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>0.055825661725382</v>
+        <v>0.05582566172538234</v>
       </c>
       <c r="E384" s="3" t="n">
-        <v>0.1566411424937055</v>
+        <v>0.1566411424937108</v>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
       <c r="G384" s="3" t="n">
-        <v>-1.416459060404555</v>
+        <v>-1.416459060404536</v>
       </c>
     </row>
     <row r="385">
@@ -20393,21 +20393,21 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>3 Hazards Combined (Log)</t>
+          <t>Poverty Gap ($4.20/day)</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
-        <v>-0.01044181699579919</v>
+        <v>-0.001599080889292452</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>0.01843032667529738</v>
+        <v>0.003539953079596808</v>
       </c>
       <c r="E385" s="3" t="n">
-        <v>0.5710156976914122</v>
+        <v>0.651468004517147</v>
       </c>
       <c r="F385" s="3" t="inlineStr"/>
       <c r="G385" s="3" t="n">
-        <v>-0.5665562623908676</v>
+        <v>-0.4517237526421067</v>
       </c>
     </row>
     <row r="386">
@@ -20422,46 +20422,46 @@
         </is>
       </c>
       <c r="C386" s="3" t="n">
-        <v>6.572744743804639e-05</v>
+        <v>6.572744743801332e-05</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>6.545555101598072e-05</v>
+        <v>6.545555101597881e-05</v>
       </c>
       <c r="E386" s="3" t="n">
-        <v>0.3153044341611392</v>
+        <v>0.3153044341613687</v>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
       <c r="G386" s="3" t="n">
-        <v>1.004153909299446</v>
+        <v>1.00415390929897</v>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="5" t="inlineStr">
+      <c r="A387" s="4" t="inlineStr">
         <is>
           <t>ONLY-M.Int.BQCI</t>
         </is>
       </c>
-      <c r="B387" s="5" t="inlineStr">
-        <is>
-          <t>Building Quality Index</t>
-        </is>
-      </c>
-      <c r="C387" s="5" t="n">
-        <v>0.01072764341142045</v>
-      </c>
-      <c r="D387" s="5" t="n">
-        <v>0.004833934816155634</v>
-      </c>
-      <c r="E387" s="5" t="n">
-        <v>0.02647065557764368</v>
-      </c>
-      <c r="F387" s="5" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="G387" s="5" t="n">
-        <v>2.219236257710237</v>
+      <c r="B387" s="4" t="inlineStr">
+        <is>
+          <t>Log GDP per Capita (PPP)</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="n">
+        <v>0.05047343018233817</v>
+      </c>
+      <c r="D387" s="4" t="n">
+        <v>0.02884807091894653</v>
+      </c>
+      <c r="E387" s="4" t="n">
+        <v>0.08018230015936906</v>
+      </c>
+      <c r="F387" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G387" s="4" t="n">
+        <v>1.749629301874351</v>
       </c>
     </row>
     <row r="388">
@@ -20472,17 +20472,17 @@
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>Log GDP per Capita (PPP)</t>
+          <t>Urban Population %</t>
         </is>
       </c>
       <c r="C388" s="4" t="n">
-        <v>0.05047343018233828</v>
+        <v>0.001922834365034254</v>
       </c>
       <c r="D388" s="4" t="n">
-        <v>0.02884807091894661</v>
+        <v>0.0009952985612107128</v>
       </c>
       <c r="E388" s="4" t="n">
-        <v>0.08018230015936925</v>
+        <v>0.05336973199198179</v>
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         </is>
       </c>
       <c r="G388" s="4" t="n">
-        <v>1.749629301874349</v>
+        <v>1.931917155285804</v>
       </c>
     </row>
     <row r="389">
@@ -20501,50 +20501,50 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>Poverty Gap ($4.20/day)</t>
+          <t>3 Hazards Combined (Log)</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>-0.001599080889292724</v>
+        <v>-0.01044181699579979</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>0.003539953079596806</v>
+        <v>0.01843032667529742</v>
       </c>
       <c r="E389" s="3" t="n">
-        <v>0.6514680045170916</v>
+        <v>0.5710156976913909</v>
       </c>
       <c r="F389" s="3" t="inlineStr"/>
       <c r="G389" s="3" t="n">
-        <v>-0.4517237526421838</v>
+        <v>-0.5665562623908991</v>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="4" t="inlineStr">
+      <c r="A390" s="5" t="inlineStr">
         <is>
           <t>ONLY-M.Int.BQCI</t>
         </is>
       </c>
-      <c r="B390" s="4" t="inlineStr">
-        <is>
-          <t>Urban Population %</t>
-        </is>
-      </c>
-      <c r="C390" s="4" t="n">
-        <v>0.001922834365034249</v>
-      </c>
-      <c r="D390" s="4" t="n">
-        <v>0.0009952985612107174</v>
-      </c>
-      <c r="E390" s="4" t="n">
-        <v>0.0533697319919835</v>
-      </c>
-      <c r="F390" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="G390" s="4" t="n">
-        <v>1.931917155285791</v>
+      <c r="B390" s="5" t="inlineStr">
+        <is>
+          <t>Building Quality Index</t>
+        </is>
+      </c>
+      <c r="C390" s="5" t="n">
+        <v>0.01072764341142059</v>
+      </c>
+      <c r="D390" s="5" t="n">
+        <v>0.004833934816155655</v>
+      </c>
+      <c r="E390" s="5" t="n">
+        <v>0.02647065557764236</v>
+      </c>
+      <c r="F390" s="5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="G390" s="5" t="n">
+        <v>2.219236257710257</v>
       </c>
     </row>
     <row r="391">
@@ -20559,17 +20559,17 @@
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>-0.001372998961028143</v>
+        <v>-0.001372998961027976</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>0.005400478703217946</v>
+        <v>0.005400478703217955</v>
       </c>
       <c r="E391" s="3" t="n">
-        <v>0.7993128313476059</v>
+        <v>0.7993128313476301</v>
       </c>
       <c r="F391" s="3" t="inlineStr"/>
       <c r="G391" s="3" t="n">
-        <v>-0.2542365291080629</v>
+        <v>-0.2542365291080315</v>
       </c>
     </row>
     <row r="392">
@@ -20584,7 +20584,7 @@
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>0.6171539965588061</v>
+        <v>0.6171539965588062</v>
       </c>
       <c r="D392" s="3" t="inlineStr"/>
       <c r="E392" s="3" t="inlineStr"/>
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>0.5805584227004567</v>
+        <v>0.5805584227004568</v>
       </c>
       <c r="D393" s="3" t="inlineStr"/>
       <c r="E393" s="3" t="inlineStr"/>
